--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EE21D7-0860-431D-91FF-236E036E477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4FCEC6-5A0E-4678-A631-53A5D699824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -560,11 +560,11 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="e">
-        <f>H2/F2</f>
+        <f t="shared" ref="G2:G33" si="1">H2/F2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H2" s="5">
-        <f>I2/3600</f>
+        <f t="shared" ref="H2:H33" si="2">I2/3600</f>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="I2" s="8">
@@ -590,18 +590,18 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="e">
-        <f>H3/F3</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H3" s="5">
-        <f>I3/3600</f>
+        <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="I3" s="8">
         <v>300</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" ref="J3:J66" si="1">I3*1000</f>
+        <f t="shared" ref="J3:J66" si="3">I3*1000</f>
         <v>300000</v>
       </c>
     </row>
@@ -620,18 +620,18 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="e">
-        <f>H4/F4</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H4" s="5">
-        <f>I4/3600</f>
+        <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="I4" s="8">
         <v>300</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300000</v>
       </c>
     </row>
@@ -650,18 +650,18 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="e">
-        <f>H5/F5</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H5" s="5">
-        <f>I5/3600</f>
+        <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="I5" s="8">
         <v>300</v>
       </c>
       <c r="J5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300000</v>
       </c>
     </row>
@@ -686,18 +686,18 @@
         <v>3.6643536711471345E-2</v>
       </c>
       <c r="G6" s="5">
-        <f>H6/F6</f>
+        <f t="shared" si="1"/>
         <v>1.6828797709191039</v>
       </c>
       <c r="H6" s="5">
-        <f>I6/3600</f>
+        <f t="shared" si="2"/>
         <v>6.1666666666666668E-2</v>
       </c>
       <c r="I6" s="8">
         <v>222</v>
       </c>
       <c r="J6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>222000</v>
       </c>
     </row>
@@ -722,18 +722,18 @@
         <v>3.6643536711471345E-2</v>
       </c>
       <c r="G7" s="5">
-        <f>H7/F7</f>
+        <f t="shared" si="1"/>
         <v>1.5540105992721454</v>
       </c>
       <c r="H7" s="5">
-        <f>I7/3600</f>
+        <f t="shared" si="2"/>
         <v>5.6944444444444443E-2</v>
       </c>
       <c r="I7" s="8">
         <v>205</v>
       </c>
       <c r="J7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>205000</v>
       </c>
     </row>
@@ -758,18 +758,18 @@
         <v>3.6643536711471345E-2</v>
       </c>
       <c r="G8" s="5">
-        <f>H8/F8</f>
+        <f t="shared" si="1"/>
         <v>1.447883046151121</v>
       </c>
       <c r="H8" s="5">
-        <f>I8/3600</f>
+        <f t="shared" si="2"/>
         <v>5.3055555555555557E-2</v>
       </c>
       <c r="I8" s="8">
         <v>191</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>191000</v>
       </c>
     </row>
@@ -794,18 +794,18 @@
         <v>3.6643536711471345E-2</v>
       </c>
       <c r="G9" s="5">
-        <f>H9/F9</f>
+        <f t="shared" si="1"/>
         <v>1.7511046264969052</v>
       </c>
       <c r="H9" s="5">
-        <f>I9/3600</f>
+        <f t="shared" si="2"/>
         <v>6.4166666666666664E-2</v>
       </c>
       <c r="I9" s="8">
         <v>231</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>231000</v>
       </c>
     </row>
@@ -830,18 +830,18 @@
         <v>3.6643536711471345E-2</v>
       </c>
       <c r="G10" s="5">
-        <f>H10/F10</f>
+        <f t="shared" si="1"/>
         <v>1.5388495202548562</v>
       </c>
       <c r="H10" s="5">
-        <f>I10/3600</f>
+        <f t="shared" si="2"/>
         <v>5.6388888888888891E-2</v>
       </c>
       <c r="I10" s="8">
         <v>203</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>203000</v>
       </c>
     </row>
@@ -866,18 +866,18 @@
         <v>3.0790749597833563E-2</v>
       </c>
       <c r="G11" s="5">
-        <f>H11/F11</f>
+        <f t="shared" si="1"/>
         <v>1.5336496460464468</v>
       </c>
       <c r="H11" s="5">
-        <f>I11/3600</f>
+        <f t="shared" si="2"/>
         <v>4.7222222222222221E-2</v>
       </c>
       <c r="I11" s="8">
         <v>170</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>170000</v>
       </c>
     </row>
@@ -902,18 +902,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G12" s="5">
-        <f>H12/F12</f>
+        <f t="shared" si="1"/>
         <v>2.9807362734323819</v>
       </c>
       <c r="H12" s="5">
-        <f>I12/3600</f>
+        <f t="shared" si="2"/>
         <v>6.1666666666666668E-2</v>
       </c>
       <c r="I12" s="8">
         <v>222</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>222000</v>
       </c>
     </row>
@@ -938,18 +938,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G13" s="5">
-        <f>H13/F13</f>
+        <f t="shared" si="1"/>
         <v>2.7524816939353074</v>
       </c>
       <c r="H13" s="5">
-        <f>I13/3600</f>
+        <f t="shared" si="2"/>
         <v>5.6944444444444443E-2</v>
       </c>
       <c r="I13" s="8">
         <v>205</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>205000</v>
       </c>
     </row>
@@ -974,18 +974,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G14" s="5">
-        <f>H14/F14</f>
+        <f t="shared" si="1"/>
         <v>2.5645073343494817</v>
       </c>
       <c r="H14" s="5">
-        <f>I14/3600</f>
+        <f t="shared" si="2"/>
         <v>5.3055555555555557E-2</v>
       </c>
       <c r="I14" s="8">
         <v>191</v>
       </c>
       <c r="J14" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>191000</v>
       </c>
     </row>
@@ -1010,18 +1010,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G15" s="5">
-        <f>H15/F15</f>
+        <f t="shared" si="1"/>
         <v>3.1015769331661267</v>
       </c>
       <c r="H15" s="5">
-        <f>I15/3600</f>
+        <f t="shared" si="2"/>
         <v>6.4166666666666664E-2</v>
       </c>
       <c r="I15" s="8">
         <v>231</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>231000</v>
       </c>
     </row>
@@ -1046,18 +1046,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G16" s="5">
-        <f>H16/F16</f>
+        <f t="shared" si="1"/>
         <v>2.7256282139944754</v>
       </c>
       <c r="H16" s="5">
-        <f>I16/3600</f>
+        <f t="shared" si="2"/>
         <v>5.6388888888888891E-2</v>
       </c>
       <c r="I16" s="8">
         <v>203</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>203000</v>
       </c>
     </row>
@@ -1076,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="G17" s="5" t="e">
-        <f>H17/F17</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H17" s="5">
-        <f>I17/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1104,18 +1104,18 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="e">
-        <f>H18/F18</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H18" s="5">
-        <f>I18/3600</f>
+        <f t="shared" si="2"/>
         <v>7.0277777777777772E-2</v>
       </c>
       <c r="I18" s="8">
         <v>253</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>253000</v>
       </c>
     </row>
@@ -1134,18 +1134,18 @@
         <v>0</v>
       </c>
       <c r="G19" s="5" t="e">
-        <f>H19/F19</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H19" s="5">
-        <f>I19/3600</f>
+        <f t="shared" si="2"/>
         <v>2.7777777777777778E-4</v>
       </c>
       <c r="I19" s="8">
         <v>1</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
@@ -1170,18 +1170,18 @@
         <v>3.5968094290949541E-2</v>
       </c>
       <c r="G20" s="5">
-        <f>H20/F20</f>
+        <f t="shared" si="1"/>
         <v>0.95763884974888747</v>
       </c>
       <c r="H20" s="5">
-        <f>I20/3600</f>
+        <f t="shared" si="2"/>
         <v>3.4444444444444444E-2</v>
       </c>
       <c r="I20" s="8">
         <v>124</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>124000</v>
       </c>
     </row>
@@ -1206,11 +1206,11 @@
         <v>3.5968094290949541E-2</v>
       </c>
       <c r="G21" s="5">
-        <f>H21/F21</f>
+        <f t="shared" si="1"/>
         <v>0.89724581906311085</v>
       </c>
       <c r="H21" s="5">
-        <f>I21/3600</f>
+        <f t="shared" si="2"/>
         <v>3.2272222222222223E-2</v>
       </c>
       <c r="I21" s="8">
@@ -1218,7 +1218,7 @@
         <v>116.18</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>116180</v>
       </c>
     </row>
@@ -1243,16 +1243,16 @@
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G22" s="5">
-        <f>H22/F22</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H22" s="5">
-        <f>I22/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1277,18 +1277,18 @@
         <v>2.068840078751958E-2</v>
       </c>
       <c r="G23" s="5">
-        <f>H23/F23</f>
+        <f t="shared" si="1"/>
         <v>0.57063644874268571</v>
       </c>
       <c r="H23" s="5">
-        <f>I23/3600</f>
+        <f t="shared" si="2"/>
         <v>1.1805555555555555E-2</v>
       </c>
       <c r="I23" s="8">
         <v>42.5</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42500</v>
       </c>
     </row>
@@ -1313,18 +1313,18 @@
         <v>3.0790749597833563E-2</v>
       </c>
       <c r="G24" s="5">
-        <f>H24/F24</f>
+        <f t="shared" si="1"/>
         <v>3.5815229969437614</v>
       </c>
       <c r="H24" s="5">
-        <f>I24/3600</f>
+        <f t="shared" si="2"/>
         <v>0.11027777777777778</v>
       </c>
       <c r="I24" s="8">
         <v>397</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>397000</v>
       </c>
     </row>
@@ -1349,18 +1349,18 @@
         <v>3.5968094290949541E-2</v>
       </c>
       <c r="G25" s="5">
-        <f>H25/F25</f>
+        <f t="shared" si="1"/>
         <v>0.25176634275656234</v>
       </c>
       <c r="H25" s="5">
-        <f>I25/3600</f>
+        <f t="shared" si="2"/>
         <v>9.0555555555555563E-3</v>
       </c>
       <c r="I25" s="8">
         <v>32.6</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32600</v>
       </c>
     </row>
@@ -1385,18 +1385,18 @@
         <v>5.5990249670440695E-2</v>
       </c>
       <c r="G26" s="5">
-        <f>H26/F26</f>
+        <f t="shared" si="1"/>
         <v>0.43162277019502443</v>
       </c>
       <c r="H26" s="5">
-        <f>I26/3600</f>
+        <f t="shared" si="2"/>
         <v>2.4166666666666666E-2</v>
       </c>
       <c r="I26" s="8">
         <v>87</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>87000</v>
       </c>
     </row>
@@ -1421,18 +1421,18 @@
         <v>1.4313881527918496E-2</v>
       </c>
       <c r="G27" s="5">
-        <f>H27/F27</f>
+        <f t="shared" si="1"/>
         <v>1.4554635856597651</v>
       </c>
       <c r="H27" s="5">
-        <f>I27/3600</f>
+        <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="I27" s="8">
         <v>75</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>75000</v>
       </c>
     </row>
@@ -1457,18 +1457,18 @@
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G28" s="5">
-        <f>H28/F28</f>
+        <f t="shared" si="1"/>
         <v>2.1192632106007938</v>
       </c>
       <c r="H28" s="5">
-        <f>I28/3600</f>
+        <f t="shared" si="2"/>
         <v>1.1438888888888889E-2</v>
       </c>
       <c r="I28" s="8">
         <v>41.18</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41180</v>
       </c>
     </row>
@@ -1487,16 +1487,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="5" t="e">
-        <f>H29/F29</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H29" s="5">
-        <f>I29/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1515,16 +1515,16 @@
         <v>0</v>
       </c>
       <c r="G30" s="5" t="e">
-        <f>H30/F30</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="5">
-        <f>I30/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1549,16 +1549,16 @@
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G31" s="5">
-        <f>H31/F31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H31" s="5">
-        <f>I31/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1583,16 +1583,16 @@
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G32" s="5">
-        <f>H32/F32</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H32" s="5">
-        <f>I32/3600</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1617,18 +1617,18 @@
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G33" s="5">
-        <f>H33/F33</f>
+        <f t="shared" si="1"/>
         <v>0.92179360425118473</v>
       </c>
       <c r="H33" s="5">
-        <f>I33/3600</f>
+        <f t="shared" si="2"/>
         <v>8.4444444444444437E-3</v>
       </c>
       <c r="I33" s="8">
         <v>30.4</v>
       </c>
       <c r="J33" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30400</v>
       </c>
     </row>
@@ -1649,22 +1649,22 @@
         <v>3</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" ref="F34:F65" si="2">(PI()/4)*((D34-2*E34)*10^-3)^2</f>
+        <f t="shared" ref="F34:F65" si="4">(PI()/4)*((D34-2*E34)*10^-3)^2</f>
         <v>3.0790749597833563E-2</v>
       </c>
       <c r="G34" s="5">
-        <f>H34/F34</f>
+        <f t="shared" ref="G34:G65" si="5">H34/F34</f>
         <v>0.50867526779290351</v>
       </c>
       <c r="H34" s="5">
-        <f>I34/3600</f>
+        <f t="shared" ref="H34:H65" si="6">I34/3600</f>
         <v>1.5662492797222222E-2</v>
       </c>
       <c r="I34" s="8">
         <v>56.384974069999998</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>56384.974069999997</v>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
         <v>3</v>
       </c>
       <c r="F35" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G35" s="5">
-        <f>H35/F35</f>
+        <f t="shared" si="5"/>
         <v>0.69999999978756267</v>
       </c>
       <c r="H35" s="5">
-        <f>I35/3600</f>
+        <f t="shared" si="6"/>
         <v>3.7783047333333334E-3</v>
       </c>
       <c r="I35" s="8">
         <v>13.601897040000001</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13601.897040000002</v>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
         <v>3</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G36" s="5">
-        <f>H36/F36</f>
+        <f t="shared" si="5"/>
         <v>1.2982213603797359</v>
       </c>
       <c r="H36" s="5">
-        <f>I36/3600</f>
+        <f t="shared" si="6"/>
         <v>3.0063413555555555E-3</v>
       </c>
       <c r="I36" s="8">
         <v>10.822828879999999</v>
       </c>
       <c r="J36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10822.828879999999</v>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
         <v>3</v>
       </c>
       <c r="F37" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
       <c r="G37" s="5">
-        <f>H37/F37</f>
+        <f t="shared" si="5"/>
         <v>0.58792361023570616</v>
       </c>
       <c r="H37" s="5">
-        <f>I37/3600</f>
+        <f t="shared" si="6"/>
         <v>2.2690643813888887E-3</v>
       </c>
       <c r="I37" s="8">
         <v>8.1686317729999995</v>
       </c>
       <c r="J37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8168.6317729999992</v>
       </c>
     </row>
@@ -1793,22 +1793,22 @@
         <v>3</v>
       </c>
       <c r="F38" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G38" s="5">
-        <f>H38/F38</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H38" s="5">
-        <f>I38/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I38" s="8">
         <v>0</v>
       </c>
       <c r="J38" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1829,22 +1829,22 @@
         <v>3</v>
       </c>
       <c r="F39" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4313881527918496E-2</v>
       </c>
       <c r="G39" s="5">
-        <f>H39/F39</f>
+        <f t="shared" si="5"/>
         <v>1.9763665296470374</v>
       </c>
       <c r="H39" s="5">
-        <f>I39/3600</f>
+        <f t="shared" si="6"/>
         <v>2.8289476361111111E-2</v>
       </c>
       <c r="I39" s="8">
         <v>101.8421149</v>
       </c>
       <c r="J39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>101842.1149</v>
       </c>
     </row>
@@ -1865,22 +1865,22 @@
         <v>3</v>
       </c>
       <c r="F40" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.5968094290949541E-2</v>
       </c>
       <c r="G40" s="5">
-        <f>H40/F40</f>
+        <f t="shared" si="5"/>
         <v>0.21624103058845845</v>
       </c>
       <c r="H40" s="5">
-        <f>I40/3600</f>
+        <f t="shared" si="6"/>
         <v>7.7777777777777776E-3</v>
       </c>
       <c r="I40" s="8">
         <v>28</v>
       </c>
       <c r="J40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28000</v>
       </c>
     </row>
@@ -1901,22 +1901,22 @@
         <v>3</v>
       </c>
       <c r="F41" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G41" s="5">
-        <f>H41/F41</f>
+        <f t="shared" si="5"/>
         <v>4.0967727478173011</v>
       </c>
       <c r="H41" s="5">
-        <f>I41/3600</f>
+        <f t="shared" si="6"/>
         <v>2.2112651241666666E-2</v>
       </c>
       <c r="I41" s="8">
         <v>79.605544469999998</v>
       </c>
       <c r="J41" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>79605.544469999993</v>
       </c>
     </row>
@@ -1937,22 +1937,22 @@
         <v>3</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G42" s="5">
-        <f>H42/F42</f>
+        <f t="shared" si="5"/>
         <v>1.1443697333909624</v>
       </c>
       <c r="H42" s="5">
-        <f>I42/3600</f>
+        <f t="shared" si="6"/>
         <v>6.1768251166666663E-3</v>
       </c>
       <c r="I42" s="8">
         <v>22.23657042</v>
       </c>
       <c r="J42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22236.57042</v>
       </c>
     </row>
@@ -1973,22 +1973,22 @@
         <v>3</v>
       </c>
       <c r="F43" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G43" s="5">
-        <f>H43/F43</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H43" s="5">
-        <f>I43/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I43" s="8">
         <v>0</v>
       </c>
       <c r="J43" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>3</v>
       </c>
       <c r="F44" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G44" s="5">
-        <f>H44/F44</f>
+        <f t="shared" si="5"/>
         <v>3.3847969636442454</v>
       </c>
       <c r="H44" s="5">
-        <f>I44/3600</f>
+        <f t="shared" si="6"/>
         <v>7.8383050861111116E-3</v>
       </c>
       <c r="I44" s="8">
         <v>28.217898309999999</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28217.89831</v>
       </c>
     </row>
@@ -2045,22 +2045,22 @@
         <v>3</v>
       </c>
       <c r="F45" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
       <c r="G45" s="5">
-        <f>H45/F45</f>
+        <f t="shared" si="5"/>
         <v>1.1041906103974501</v>
       </c>
       <c r="H45" s="5">
-        <f>I45/3600</f>
+        <f t="shared" si="6"/>
         <v>4.2615733416666666E-3</v>
       </c>
       <c r="I45" s="8">
         <v>15.34166403</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>15341.66403</v>
       </c>
     </row>
@@ -2081,22 +2081,22 @@
         <v>3</v>
       </c>
       <c r="F46" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
       <c r="G46" s="5">
-        <f>H46/F46</f>
+        <f t="shared" si="5"/>
         <v>1.0003778179300111</v>
       </c>
       <c r="H46" s="5">
-        <f>I46/3600</f>
+        <f t="shared" si="6"/>
         <v>3.8609126E-3</v>
       </c>
       <c r="I46" s="8">
         <v>13.89928536</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13899.28536</v>
       </c>
     </row>
@@ -2117,22 +2117,22 @@
         <v>3</v>
       </c>
       <c r="F47" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G47" s="5">
-        <f>H47/F47</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H47" s="5">
-        <f>I47/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I47" s="8">
         <v>0</v>
       </c>
       <c r="J47" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2153,22 +2153,22 @@
         <v>3</v>
       </c>
       <c r="F48" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G48" s="5">
-        <f>H48/F48</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H48" s="5">
-        <f>I48/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I48" s="8">
         <v>0</v>
       </c>
       <c r="J48" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2189,22 +2189,22 @@
         <v>3</v>
       </c>
       <c r="F49" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0292171692425523E-3</v>
       </c>
       <c r="G49" s="5">
-        <f>H49/F49</f>
+        <f t="shared" si="5"/>
         <v>0.31745062740409141</v>
       </c>
       <c r="H49" s="5">
-        <f>I49/3600</f>
+        <f t="shared" si="6"/>
         <v>3.2672563611111115E-4</v>
       </c>
       <c r="I49" s="8">
         <v>1.17621229</v>
       </c>
       <c r="J49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1176.2122899999999</v>
       </c>
     </row>
@@ -2225,22 +2225,22 @@
         <v>3</v>
       </c>
       <c r="F50" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G50" s="5">
-        <f>H50/F50</f>
+        <f t="shared" si="5"/>
         <v>0.52441647116270518</v>
       </c>
       <c r="H50" s="5">
-        <f>I50/3600</f>
+        <f t="shared" si="6"/>
         <v>2.8305789083333333E-3</v>
       </c>
       <c r="I50" s="8">
         <v>10.190084069999999</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10190.084069999999</v>
       </c>
     </row>
@@ -2261,22 +2261,22 @@
         <v>3</v>
       </c>
       <c r="F51" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
       <c r="G51" s="5">
-        <f>H51/F51</f>
+        <f t="shared" si="5"/>
         <v>0.64898914116708672</v>
       </c>
       <c r="H51" s="5">
-        <f>I51/3600</f>
+        <f t="shared" si="6"/>
         <v>9.1115051749999995E-3</v>
       </c>
       <c r="I51" s="8">
         <v>32.801418630000001</v>
       </c>
       <c r="J51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32801.41863</v>
       </c>
     </row>
@@ -2297,22 +2297,22 @@
         <v>3</v>
       </c>
       <c r="F52" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G52" s="5">
-        <f>H52/F52</f>
+        <f t="shared" si="5"/>
         <v>1.2982213603797359</v>
       </c>
       <c r="H52" s="5">
-        <f>I52/3600</f>
+        <f t="shared" si="6"/>
         <v>3.0063413555555555E-3</v>
       </c>
       <c r="I52" s="8">
         <v>10.822828879999999</v>
       </c>
       <c r="J52" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10822.828879999999</v>
       </c>
     </row>
@@ -2333,22 +2333,22 @@
         <v>3</v>
       </c>
       <c r="F53" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G53" s="5">
-        <f>H53/F53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H53" s="5">
-        <f>I53/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I53" s="8">
         <v>0</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2369,20 +2369,20 @@
         <v>3</v>
       </c>
       <c r="F54" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0752100856911066E-3</v>
       </c>
       <c r="G54" s="5">
-        <f>H54/F54</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H54" s="5">
-        <f>I54/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2403,20 +2403,20 @@
         <v>3</v>
       </c>
       <c r="F55" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4053050797854202E-3</v>
       </c>
       <c r="G55" s="5">
-        <f>H55/F55</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H55" s="5">
-        <f>I55/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2437,20 +2437,20 @@
         <v>3</v>
       </c>
       <c r="F56" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G56" s="5">
-        <f>H56/F56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H56" s="5">
-        <f>I56/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2471,22 +2471,22 @@
         <v>3</v>
       </c>
       <c r="F57" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G57" s="5">
-        <f>H57/F57</f>
+        <f t="shared" si="5"/>
         <v>0.97984476797762998</v>
       </c>
       <c r="H57" s="5">
-        <f>I57/3600</f>
+        <f t="shared" si="6"/>
         <v>2.2690643813888887E-3</v>
       </c>
       <c r="I57" s="8">
         <v>8.1686317729999995</v>
       </c>
       <c r="J57" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8168.6317729999992</v>
       </c>
     </row>
@@ -2507,22 +2507,22 @@
         <v>3</v>
       </c>
       <c r="F58" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G58" s="5">
-        <f>H58/F58</f>
+        <f t="shared" si="5"/>
         <v>5.1463409679475318E-2</v>
       </c>
       <c r="H58" s="5">
-        <f>I58/3600</f>
+        <f t="shared" si="6"/>
         <v>2.7777777777777778E-4</v>
       </c>
       <c r="I58" s="8">
         <v>1</v>
       </c>
       <c r="J58" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
@@ -2543,22 +2543,22 @@
         <v>3</v>
       </c>
       <c r="F59" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G59" s="5">
-        <f>H59/F59</f>
+        <f t="shared" si="5"/>
         <v>0.11995212848452021</v>
       </c>
       <c r="H59" s="5">
-        <f>I59/3600</f>
+        <f t="shared" si="6"/>
         <v>2.7777777777777778E-4</v>
       </c>
       <c r="I59" s="8">
         <v>1</v>
       </c>
       <c r="J59" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
@@ -2579,20 +2579,20 @@
         <v>3</v>
       </c>
       <c r="F60" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G60" s="5">
-        <f>H60/F60</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H60" s="5">
-        <f>I60/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2613,20 +2613,20 @@
         <v>3</v>
       </c>
       <c r="F61" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
       <c r="G61" s="5">
-        <f>H61/F61</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H61" s="5">
-        <f>I61/3600</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2647,22 +2647,22 @@
         <v>3</v>
       </c>
       <c r="F62" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.5256523554911458E-3</v>
       </c>
       <c r="G62" s="5">
-        <f>H62/F62</f>
+        <f t="shared" si="5"/>
         <v>1.3500000001822385</v>
       </c>
       <c r="H62" s="5">
-        <f>I62/3600</f>
+        <f t="shared" si="6"/>
         <v>4.7596306805555563E-3</v>
       </c>
       <c r="I62" s="8">
         <v>17.134670450000002</v>
       </c>
       <c r="J62" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17134.670450000001</v>
       </c>
     </row>
@@ -2683,22 +2683,22 @@
         <v>3</v>
       </c>
       <c r="F63" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
       <c r="G63" s="5">
-        <f>H63/F63</f>
+        <f t="shared" si="5"/>
         <v>1.8267449193391221</v>
       </c>
       <c r="H63" s="5">
-        <f>I63/3600</f>
+        <f t="shared" si="6"/>
         <v>7.0502387694444443E-3</v>
       </c>
       <c r="I63" s="8">
         <v>25.380859569999998</v>
       </c>
       <c r="J63" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25380.859569999997</v>
       </c>
     </row>
@@ -2719,22 +2719,22 @@
         <v>3</v>
       </c>
       <c r="F64" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
       <c r="G64" s="5">
-        <f>H64/F64</f>
+        <f t="shared" si="5"/>
         <v>2.9678097850935239</v>
       </c>
       <c r="H64" s="5">
-        <f>I64/3600</f>
+        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I64" s="8">
         <v>150</v>
       </c>
       <c r="J64" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>150000</v>
       </c>
     </row>
@@ -2755,22 +2755,22 @@
         <v>3</v>
       </c>
       <c r="F65" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
       <c r="G65" s="5">
-        <f>H65/F65</f>
+        <f t="shared" si="5"/>
         <v>0.8705575369607671</v>
       </c>
       <c r="H65" s="5">
-        <f>I65/3600</f>
+        <f t="shared" si="6"/>
         <v>1.2222222222222223E-2</v>
       </c>
       <c r="I65" s="8">
         <v>44</v>
       </c>
       <c r="J65" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44000</v>
       </c>
     </row>
@@ -2791,22 +2791,22 @@
         <v>3</v>
       </c>
       <c r="F66" s="5">
-        <f t="shared" ref="F66:F72" si="3">(PI()/4)*((D66-2*E66)*10^-3)^2</f>
+        <f t="shared" ref="F66:F72" si="7">(PI()/4)*((D66-2*E66)*10^-3)^2</f>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G66" s="5">
-        <f>H66/F66</f>
+        <f t="shared" ref="G66:G97" si="8">H66/F66</f>
         <v>2.4187802549353399</v>
       </c>
       <c r="H66" s="5">
-        <f>I66/3600</f>
+        <f t="shared" ref="H66:H97" si="9">I66/3600</f>
         <v>1.3055555555555556E-2</v>
       </c>
       <c r="I66" s="8">
         <v>47</v>
       </c>
       <c r="J66" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>47000</v>
       </c>
     </row>
@@ -2827,22 +2827,22 @@
         <v>3</v>
       </c>
       <c r="F67" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G67" s="5">
-        <f>H67/F67</f>
+        <f t="shared" si="8"/>
         <v>3.4480484485248462</v>
       </c>
       <c r="H67" s="5">
-        <f>I67/3600</f>
+        <f t="shared" si="9"/>
         <v>1.861111111111111E-2</v>
       </c>
       <c r="I67" s="8">
         <v>67</v>
       </c>
       <c r="J67" s="4">
-        <f t="shared" ref="J67:J72" si="4">I67*1000</f>
+        <f t="shared" ref="J67:J72" si="10">I67*1000</f>
         <v>67000</v>
       </c>
     </row>
@@ -2863,22 +2863,22 @@
         <v>3</v>
       </c>
       <c r="F68" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.3975781921142578E-3</v>
       </c>
       <c r="G68" s="5">
-        <f>H68/F68</f>
+        <f t="shared" si="8"/>
         <v>0.2270819116024291</v>
       </c>
       <c r="H68" s="5">
-        <f>I68/3600</f>
+        <f t="shared" si="9"/>
         <v>1.225692373888889E-3</v>
       </c>
       <c r="I68" s="8">
         <v>4.4124925460000002</v>
       </c>
       <c r="J68" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>4412.4925460000004</v>
       </c>
     </row>
@@ -2899,22 +2899,22 @@
         <v>3</v>
       </c>
       <c r="F69" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.8594544289166943E-3</v>
       </c>
       <c r="G69" s="5">
-        <f>H69/F69</f>
+        <f t="shared" si="8"/>
         <v>0.89981501849423517</v>
       </c>
       <c r="H69" s="5">
-        <f>I69/3600</f>
+        <f t="shared" si="9"/>
         <v>3.4727950583333333E-3</v>
       </c>
       <c r="I69" s="8">
         <v>12.50206221</v>
       </c>
       <c r="J69" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>12502.06221</v>
       </c>
     </row>
@@ -2935,22 +2935,22 @@
         <v>3</v>
       </c>
       <c r="F70" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1882288814039995E-2</v>
       </c>
       <c r="G70" s="5">
-        <f>H70/F70</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H70" s="5">
-        <f>I70/3600</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I70" s="8">
         <v>0</v>
       </c>
       <c r="J70" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2971,22 +2971,22 @@
         <v>3</v>
       </c>
       <c r="F71" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1882288814039995E-2</v>
       </c>
       <c r="G71" s="5">
-        <f>H71/F71</f>
+        <f t="shared" si="8"/>
         <v>1.7533097923622991</v>
       </c>
       <c r="H71" s="5">
-        <f>I71/3600</f>
+        <f t="shared" si="9"/>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="I71" s="8">
         <v>75</v>
       </c>
       <c r="J71" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>75000</v>
       </c>
     </row>
@@ -3007,22 +3007,22 @@
         <v>3</v>
       </c>
       <c r="F72" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>9.1608841778678361E-3</v>
       </c>
       <c r="G72" s="5">
-        <f>H72/F72</f>
+        <f t="shared" si="8"/>
         <v>2.1831953784896481</v>
       </c>
       <c r="H72" s="5">
-        <f>I72/3600</f>
+        <f t="shared" si="9"/>
         <v>0.02</v>
       </c>
       <c r="I72" s="8">
         <v>72</v>
       </c>
       <c r="J72" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>72000</v>
       </c>
     </row>

--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4FCEC6-5A0E-4678-A631-53A5D699824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ABDE0B-39C0-406D-B0B7-AFFB5102BCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="82">
   <si>
     <t>source</t>
   </si>
@@ -267,6 +267,21 @@
   </si>
   <si>
     <t>cabal kgh</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>yellow</t>
   </si>
 </sst>
 </file>
@@ -502,18 +517,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="2"/>
-    <col min="3" max="5" width="11.5546875" style="11"/>
-    <col min="6" max="8" width="11.5546875" style="2"/>
-    <col min="9" max="9" width="11.5546875" style="11"/>
-    <col min="10" max="16384" width="11.5546875" style="2"/>
+    <col min="2" max="3" width="11.5546875" style="2"/>
+    <col min="4" max="6" width="11.5546875" style="11"/>
+    <col min="7" max="9" width="11.5546875" style="2"/>
+    <col min="10" max="10" width="11.5546875" style="11"/>
+    <col min="11" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -521,3416 +536,3750 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="C2" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
-      <c r="F2" s="5">
-        <f t="shared" ref="F2:F33" si="0">(PI()/4)*((D2-2*E2)*10^-3)^2</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="e">
-        <f t="shared" ref="G2:G33" si="1">H2/F2</f>
+      <c r="F2" s="8"/>
+      <c r="G2" s="5">
+        <f t="shared" ref="G2:G33" si="0">(PI()/4)*((E2-2*F2)*10^-3)^2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="e">
+        <f t="shared" ref="H2:H33" si="1">I2/G2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H2" s="5">
-        <f t="shared" ref="H2:H33" si="2">I2/3600</f>
+      <c r="I2" s="5">
+        <f t="shared" ref="I2:I33" si="2">J2/3600</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I2" s="8">
+      <c r="J2" s="8">
         <v>300</v>
       </c>
-      <c r="J2" s="4">
-        <f>I2*1000</f>
+      <c r="K2" s="4">
+        <f>J2*1000</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="5">
+      <c r="F3" s="8"/>
+      <c r="G3" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G3" s="5" t="e">
+      <c r="H3" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H3" s="5">
+      <c r="I3" s="5">
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I3" s="8">
+      <c r="J3" s="8">
         <v>300</v>
       </c>
-      <c r="J3" s="4">
-        <f t="shared" ref="J3:J66" si="3">I3*1000</f>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K66" si="3">J3*1000</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="5">
+      <c r="F4" s="8"/>
+      <c r="G4" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="e">
+      <c r="H4" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="8">
         <v>300</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <f t="shared" si="3"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="8"/>
+      <c r="C5" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="5">
+      <c r="F5" s="8"/>
+      <c r="G5" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="e">
+      <c r="H5" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="J5" s="8">
         <v>300</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <f t="shared" si="3"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="8">
         <v>200</v>
       </c>
-      <c r="D6" s="9">
+      <c r="E6" s="9">
         <v>222</v>
       </c>
-      <c r="E6" s="8">
-        <v>3</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="F6" s="8">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
         <f t="shared" si="0"/>
         <v>3.6643536711471345E-2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
         <v>1.6828797709191039</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <f t="shared" si="2"/>
         <v>6.1666666666666668E-2</v>
       </c>
-      <c r="I6" s="8">
+      <c r="J6" s="8">
         <v>222</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <f t="shared" si="3"/>
         <v>222000</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="8">
         <v>200</v>
       </c>
-      <c r="D7" s="9">
+      <c r="E7" s="9">
         <v>222</v>
       </c>
-      <c r="E7" s="8">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="F7" s="8">
+        <v>3</v>
+      </c>
+      <c r="G7" s="5">
         <f t="shared" si="0"/>
         <v>3.6643536711471345E-2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="5">
         <f t="shared" si="1"/>
         <v>1.5540105992721454</v>
       </c>
-      <c r="H7" s="5">
+      <c r="I7" s="5">
         <f t="shared" si="2"/>
         <v>5.6944444444444443E-2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="8">
         <v>205</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <f t="shared" si="3"/>
         <v>205000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="8">
         <v>200</v>
       </c>
-      <c r="D8" s="9">
+      <c r="E8" s="9">
         <v>222</v>
       </c>
-      <c r="E8" s="8">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="F8" s="8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
         <f t="shared" si="0"/>
         <v>3.6643536711471345E-2</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="5">
         <f t="shared" si="1"/>
         <v>1.447883046151121</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <f t="shared" si="2"/>
         <v>5.3055555555555557E-2</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J8" s="8">
         <v>191</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <f t="shared" si="3"/>
         <v>191000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="8">
         <v>200</v>
       </c>
-      <c r="D9" s="9">
+      <c r="E9" s="9">
         <v>222</v>
       </c>
-      <c r="E9" s="8">
-        <v>3</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="F9" s="8">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5">
         <f t="shared" si="0"/>
         <v>3.6643536711471345E-2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>1.7511046264969052</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <f t="shared" si="2"/>
         <v>6.4166666666666664E-2</v>
       </c>
-      <c r="I9" s="8">
+      <c r="J9" s="8">
         <v>231</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <f t="shared" si="3"/>
         <v>231000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="8">
         <v>200</v>
       </c>
-      <c r="D10" s="9">
+      <c r="E10" s="9">
         <v>222</v>
       </c>
-      <c r="E10" s="8">
-        <v>3</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="F10" s="8">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
         <f t="shared" si="0"/>
         <v>3.6643536711471345E-2</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="5">
         <f t="shared" si="1"/>
         <v>1.5388495202548562</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <f t="shared" si="2"/>
         <v>5.6388888888888891E-2</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="8">
         <v>203</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <f t="shared" si="3"/>
         <v>203000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="8">
-        <v>204</v>
+      <c r="C11" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="D11" s="8">
         <v>204</v>
       </c>
       <c r="E11" s="8">
-        <v>3</v>
-      </c>
-      <c r="F11" s="5">
+        <v>204</v>
+      </c>
+      <c r="F11" s="8">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
         <f t="shared" si="0"/>
         <v>3.0790749597833563E-2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="5">
         <f t="shared" si="1"/>
         <v>1.5336496460464468</v>
       </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <f t="shared" si="2"/>
         <v>4.7222222222222221E-2</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <v>170</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <f t="shared" si="3"/>
         <v>170000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="8">
         <v>150</v>
       </c>
-      <c r="D12" s="8">
+      <c r="E12" s="8">
         <v>168.3</v>
       </c>
-      <c r="E12" s="8">
-        <v>3</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="F12" s="8">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="5">
         <f t="shared" si="1"/>
         <v>2.9807362734323819</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <f t="shared" si="2"/>
         <v>6.1666666666666668E-2</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="8">
         <v>222</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <f t="shared" si="3"/>
         <v>222000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="8">
         <v>150</v>
       </c>
-      <c r="D13" s="8">
+      <c r="E13" s="8">
         <v>168.3</v>
       </c>
-      <c r="E13" s="8">
-        <v>3</v>
-      </c>
-      <c r="F13" s="5">
+      <c r="F13" s="8">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>2.7524816939353074</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <f t="shared" si="2"/>
         <v>5.6944444444444443E-2</v>
       </c>
-      <c r="I13" s="8">
+      <c r="J13" s="8">
         <v>205</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <f t="shared" si="3"/>
         <v>205000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="8">
         <v>150</v>
       </c>
-      <c r="D14" s="8">
+      <c r="E14" s="8">
         <v>168.3</v>
       </c>
-      <c r="E14" s="8">
-        <v>3</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="F14" s="8">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G14" s="5">
+      <c r="H14" s="5">
         <f t="shared" si="1"/>
         <v>2.5645073343494817</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <f t="shared" si="2"/>
         <v>5.3055555555555557E-2</v>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="8">
         <v>191</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <f t="shared" si="3"/>
         <v>191000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="8">
         <v>150</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="8">
         <v>168.3</v>
       </c>
-      <c r="E15" s="8">
-        <v>3</v>
-      </c>
-      <c r="F15" s="5">
+      <c r="F15" s="8">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G15" s="5">
+      <c r="H15" s="5">
         <f t="shared" si="1"/>
         <v>3.1015769331661267</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <f t="shared" si="2"/>
         <v>6.4166666666666664E-2</v>
       </c>
-      <c r="I15" s="8">
+      <c r="J15" s="8">
         <v>231</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <f t="shared" si="3"/>
         <v>231000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="8">
         <v>150</v>
       </c>
-      <c r="D16" s="8">
+      <c r="E16" s="8">
         <v>168.3</v>
       </c>
-      <c r="E16" s="8">
-        <v>3</v>
-      </c>
-      <c r="F16" s="5">
+      <c r="F16" s="8">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="H16" s="5">
         <f t="shared" si="1"/>
         <v>2.7256282139944754</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <f t="shared" si="2"/>
         <v>5.6388888888888891E-2</v>
       </c>
-      <c r="I16" s="8">
+      <c r="J16" s="8">
         <v>203</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <f t="shared" si="3"/>
         <v>203000</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="8"/>
+      <c r="C17" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="5">
+      <c r="F17" s="8"/>
+      <c r="G17" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="5" t="e">
+      <c r="H17" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J17" s="8"/>
+      <c r="K17" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="8"/>
+      <c r="C18" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="5">
+      <c r="F18" s="8"/>
+      <c r="G18" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="5" t="e">
+      <c r="H18" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <f t="shared" si="2"/>
         <v>7.0277777777777772E-2</v>
       </c>
-      <c r="I18" s="8">
+      <c r="J18" s="8">
         <v>253</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <f t="shared" si="3"/>
         <v>253000</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="8"/>
+      <c r="C19" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="5">
+      <c r="F19" s="8"/>
+      <c r="G19" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="5" t="e">
+      <c r="H19" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="5">
+      <c r="I19" s="5">
         <f t="shared" si="2"/>
         <v>2.7777777777777778E-4</v>
       </c>
-      <c r="I19" s="8">
+      <c r="J19" s="8">
         <v>1</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="8">
         <v>200</v>
       </c>
-      <c r="D20" s="8">
+      <c r="E20" s="8">
         <v>220</v>
       </c>
-      <c r="E20" s="8">
-        <v>3</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="F20" s="8">
+        <v>3</v>
+      </c>
+      <c r="G20" s="5">
         <f t="shared" si="0"/>
         <v>3.5968094290949541E-2</v>
       </c>
-      <c r="G20" s="5">
+      <c r="H20" s="5">
         <f t="shared" si="1"/>
         <v>0.95763884974888747</v>
       </c>
-      <c r="H20" s="5">
+      <c r="I20" s="5">
         <f t="shared" si="2"/>
         <v>3.4444444444444444E-2</v>
       </c>
-      <c r="I20" s="8">
+      <c r="J20" s="8">
         <v>124</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <f t="shared" si="3"/>
         <v>124000</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="8">
         <v>200</v>
       </c>
-      <c r="D21" s="8">
+      <c r="E21" s="8">
         <v>220</v>
       </c>
-      <c r="E21" s="8">
-        <v>3</v>
-      </c>
-      <c r="F21" s="5">
+      <c r="F21" s="8">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5">
         <f t="shared" si="0"/>
         <v>3.5968094290949541E-2</v>
       </c>
-      <c r="G21" s="5">
+      <c r="H21" s="5">
         <f t="shared" si="1"/>
-        <v>0.89724581906311085</v>
-      </c>
-      <c r="H21" s="5">
+        <v>1.2138844709962109</v>
+      </c>
+      <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>3.2272222222222223E-2</v>
-      </c>
-      <c r="I21" s="8">
-        <f>75+41.18</f>
-        <v>116.18</v>
-      </c>
-      <c r="J21" s="4">
-        <f t="shared" si="3"/>
-        <v>116180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>4.3661111111111116E-2</v>
+      </c>
+      <c r="J21" s="8">
+        <f>75+41.18+J31</f>
+        <v>157.18</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="3"/>
+        <v>157180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="8">
         <v>100</v>
       </c>
-      <c r="D22" s="8">
+      <c r="E22" s="8">
         <v>114</v>
       </c>
-      <c r="E22" s="8">
-        <v>3</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="F22" s="8">
+        <v>3</v>
+      </c>
+      <c r="G22" s="5">
         <f t="shared" si="0"/>
         <v>9.1608841778678361E-3</v>
       </c>
-      <c r="G22" s="5">
+      <c r="H22" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H22" s="5">
+      <c r="I22" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J22" s="8"/>
+      <c r="K22" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="8">
         <v>150</v>
       </c>
-      <c r="D23" s="8">
+      <c r="E23" s="8">
         <v>168.3</v>
       </c>
-      <c r="E23" s="8">
-        <v>3</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="F23" s="8">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5">
         <f t="shared" si="0"/>
         <v>2.068840078751958E-2</v>
       </c>
-      <c r="G23" s="5">
+      <c r="H23" s="5">
         <f t="shared" si="1"/>
         <v>0.57063644874268571</v>
       </c>
-      <c r="H23" s="5">
+      <c r="I23" s="5">
         <f t="shared" si="2"/>
         <v>1.1805555555555555E-2</v>
       </c>
-      <c r="I23" s="8">
+      <c r="J23" s="8">
         <v>42.5</v>
       </c>
-      <c r="J23" s="4">
+      <c r="K23" s="4">
         <f t="shared" si="3"/>
         <v>42500</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="8">
-        <v>204</v>
+      <c r="C24" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D24" s="8">
         <v>204</v>
       </c>
       <c r="E24" s="8">
-        <v>3</v>
-      </c>
-      <c r="F24" s="5">
+        <v>204</v>
+      </c>
+      <c r="F24" s="8">
+        <v>3</v>
+      </c>
+      <c r="G24" s="5">
         <f t="shared" si="0"/>
         <v>3.0790749597833563E-2</v>
       </c>
-      <c r="G24" s="5">
+      <c r="H24" s="5">
         <f t="shared" si="1"/>
         <v>3.5815229969437614</v>
       </c>
-      <c r="H24" s="5">
+      <c r="I24" s="5">
         <f t="shared" si="2"/>
         <v>0.11027777777777778</v>
       </c>
-      <c r="I24" s="8">
+      <c r="J24" s="8">
         <v>397</v>
       </c>
-      <c r="J24" s="4">
+      <c r="K24" s="4">
         <f t="shared" si="3"/>
         <v>397000</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="8">
         <v>200</v>
       </c>
-      <c r="D25" s="8">
+      <c r="E25" s="8">
         <v>220</v>
       </c>
-      <c r="E25" s="8">
-        <v>3</v>
-      </c>
-      <c r="F25" s="5">
+      <c r="F25" s="8">
+        <v>3</v>
+      </c>
+      <c r="G25" s="5">
         <f t="shared" si="0"/>
         <v>3.5968094290949541E-2</v>
       </c>
-      <c r="G25" s="5">
+      <c r="H25" s="5">
         <f t="shared" si="1"/>
         <v>0.25176634275656234</v>
       </c>
-      <c r="H25" s="5">
+      <c r="I25" s="5">
         <f t="shared" si="2"/>
         <v>9.0555555555555563E-3</v>
       </c>
-      <c r="I25" s="8">
+      <c r="J25" s="8">
         <v>32.6</v>
       </c>
-      <c r="J25" s="4">
+      <c r="K25" s="4">
         <f t="shared" si="3"/>
         <v>32600</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="8">
         <v>250</v>
       </c>
-      <c r="D26" s="8">
+      <c r="E26" s="8">
         <v>273</v>
       </c>
-      <c r="E26" s="8">
-        <v>3</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="F26" s="8">
+        <v>3</v>
+      </c>
+      <c r="G26" s="5">
         <f t="shared" si="0"/>
         <v>5.5990249670440695E-2</v>
       </c>
-      <c r="G26" s="5">
+      <c r="H26" s="5">
         <f t="shared" si="1"/>
         <v>0.43162277019502443</v>
       </c>
-      <c r="H26" s="5">
+      <c r="I26" s="5">
         <f t="shared" si="2"/>
         <v>2.4166666666666666E-2</v>
       </c>
-      <c r="I26" s="8">
+      <c r="J26" s="8">
         <v>87</v>
       </c>
-      <c r="J26" s="4">
+      <c r="K26" s="4">
         <f t="shared" si="3"/>
         <v>87000</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="8">
         <v>125</v>
       </c>
-      <c r="D27" s="8">
+      <c r="E27" s="8">
         <v>141</v>
       </c>
-      <c r="E27" s="8">
-        <v>3</v>
-      </c>
-      <c r="F27" s="5">
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+      <c r="G27" s="5">
         <f t="shared" si="0"/>
         <v>1.4313881527918496E-2</v>
       </c>
-      <c r="G27" s="5">
+      <c r="H27" s="5">
         <f t="shared" si="1"/>
         <v>1.4554635856597651</v>
       </c>
-      <c r="H27" s="5">
+      <c r="I27" s="5">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="I27" s="8">
+      <c r="J27" s="8">
         <v>75</v>
       </c>
-      <c r="J27" s="4">
+      <c r="K27" s="4">
         <f t="shared" si="3"/>
         <v>75000</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="8">
         <v>80</v>
       </c>
-      <c r="D28" s="8">
+      <c r="E28" s="8">
         <v>88.9</v>
       </c>
-      <c r="E28" s="8">
-        <v>3</v>
-      </c>
-      <c r="F28" s="5">
+      <c r="F28" s="8">
+        <v>3</v>
+      </c>
+      <c r="G28" s="5">
+        <f>(PI()/4)*((E28-2*F28)*10^-3)^2</f>
+        <v>5.3975781921142578E-3</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0292681935895065</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="2"/>
+        <v>5.5555555555555558E-3</v>
+      </c>
+      <c r="J28" s="8">
+        <v>20</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" si="3"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="str">
+        <f>A68</f>
+        <v>EI-7x2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="8">
+        <v>100</v>
+      </c>
+      <c r="E31" s="8">
+        <v>114</v>
+      </c>
+      <c r="F31" s="8">
+        <v>3</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="0"/>
+        <v>9.1608841778678361E-3</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2432084794177163</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="2"/>
+        <v>1.1388888888888889E-2</v>
+      </c>
+      <c r="J31" s="8">
+        <v>41</v>
+      </c>
+      <c r="K31" s="4">
+        <f t="shared" si="3"/>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="8">
+        <v>80</v>
+      </c>
+      <c r="E32" s="8">
+        <v>88.9</v>
+      </c>
+      <c r="F32" s="8">
+        <v>3</v>
+      </c>
+      <c r="G32" s="5">
         <f t="shared" si="0"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G28" s="5">
+      <c r="H32" s="5">
         <f t="shared" si="1"/>
-        <v>2.1192632106007938</v>
-      </c>
-      <c r="H28" s="5">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>1.1438888888888889E-2</v>
-      </c>
-      <c r="I28" s="8">
-        <v>41.18</v>
-      </c>
-      <c r="J28" s="4">
-        <f t="shared" si="3"/>
-        <v>41180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H29" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="8"/>
-      <c r="J29" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H30" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="8">
         <v>100</v>
       </c>
-      <c r="D31" s="8">
+      <c r="E33" s="8">
         <v>114</v>
       </c>
-      <c r="E31" s="8">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5">
+      <c r="F33" s="8">
+        <v>3</v>
+      </c>
+      <c r="G33" s="5">
         <f t="shared" si="0"/>
         <v>9.1608841778678361E-3</v>
       </c>
-      <c r="G31" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="8">
-        <v>80</v>
-      </c>
-      <c r="D32" s="8">
-        <v>88.9</v>
-      </c>
-      <c r="E32" s="8">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5">
-        <f t="shared" si="0"/>
-        <v>5.3975781921142578E-3</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="8">
-        <v>100</v>
-      </c>
-      <c r="D33" s="8">
-        <v>114</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3</v>
-      </c>
-      <c r="F33" s="5">
-        <f t="shared" si="0"/>
-        <v>9.1608841778678361E-3</v>
-      </c>
-      <c r="G33" s="5">
+      <c r="H33" s="5">
         <f t="shared" si="1"/>
         <v>0.92179360425118473</v>
       </c>
-      <c r="H33" s="5">
+      <c r="I33" s="5">
         <f t="shared" si="2"/>
         <v>8.4444444444444437E-3</v>
       </c>
-      <c r="I33" s="8">
+      <c r="J33" s="8">
         <v>30.4</v>
       </c>
-      <c r="J33" s="4">
+      <c r="K33" s="4">
         <f t="shared" si="3"/>
         <v>30400</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="8">
-        <v>204</v>
+      <c r="C34" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D34" s="8">
         <v>204</v>
       </c>
       <c r="E34" s="8">
-        <v>3</v>
-      </c>
-      <c r="F34" s="5">
-        <f t="shared" ref="F34:F65" si="4">(PI()/4)*((D34-2*E34)*10^-3)^2</f>
+        <v>204</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" ref="G34:G65" si="4">(PI()/4)*((E34-2*F34)*10^-3)^2</f>
         <v>3.0790749597833563E-2</v>
       </c>
-      <c r="G34" s="5">
-        <f t="shared" ref="G34:G65" si="5">H34/F34</f>
+      <c r="H34" s="5">
+        <f t="shared" ref="H34:H65" si="5">I34/G34</f>
         <v>0.50867526779290351</v>
       </c>
-      <c r="H34" s="5">
-        <f t="shared" ref="H34:H65" si="6">I34/3600</f>
+      <c r="I34" s="5">
+        <f t="shared" ref="I34:I65" si="6">J34/3600</f>
         <v>1.5662492797222222E-2</v>
       </c>
-      <c r="I34" s="8">
+      <c r="J34" s="8">
         <v>56.384974069999998</v>
       </c>
-      <c r="J34" s="4">
+      <c r="K34" s="4">
         <f t="shared" si="3"/>
         <v>56384.974069999997</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="8">
         <v>80</v>
       </c>
-      <c r="D35" s="8">
+      <c r="E35" s="8">
         <v>88.9</v>
       </c>
-      <c r="E35" s="8">
-        <v>3</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
+      <c r="G35" s="5">
         <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G35" s="5">
+      <c r="H35" s="5">
         <f t="shared" si="5"/>
         <v>0.69999999978756267</v>
       </c>
-      <c r="H35" s="5">
+      <c r="I35" s="5">
         <f t="shared" si="6"/>
         <v>3.7783047333333334E-3</v>
       </c>
-      <c r="I35" s="8">
+      <c r="J35" s="8">
         <v>13.601897040000001</v>
       </c>
-      <c r="J35" s="4">
+      <c r="K35" s="4">
         <f t="shared" si="3"/>
         <v>13601.897040000002</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="8">
         <v>50</v>
       </c>
-      <c r="D36" s="8">
+      <c r="E36" s="8">
         <v>60.3</v>
       </c>
-      <c r="E36" s="8">
-        <v>3</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="F36" s="8">
+        <v>3</v>
+      </c>
+      <c r="G36" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G36" s="5">
+      <c r="H36" s="5">
         <f t="shared" si="5"/>
         <v>1.2982213603797359</v>
       </c>
-      <c r="H36" s="5">
+      <c r="I36" s="5">
         <f t="shared" si="6"/>
         <v>3.0063413555555555E-3</v>
       </c>
-      <c r="I36" s="8">
+      <c r="J36" s="8">
         <v>10.822828879999999</v>
       </c>
-      <c r="J36" s="4">
+      <c r="K36" s="4">
         <f t="shared" si="3"/>
         <v>10822.828879999999</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="8">
         <v>65</v>
       </c>
-      <c r="D37" s="8">
+      <c r="E37" s="8">
         <v>76.099999999999994</v>
       </c>
-      <c r="E37" s="8">
-        <v>3</v>
-      </c>
-      <c r="F37" s="5">
+      <c r="F37" s="8">
+        <v>3</v>
+      </c>
+      <c r="G37" s="5">
         <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
-      <c r="G37" s="5">
+      <c r="H37" s="5">
         <f t="shared" si="5"/>
         <v>0.58792361023570616</v>
       </c>
-      <c r="H37" s="5">
+      <c r="I37" s="5">
         <f t="shared" si="6"/>
         <v>2.2690643813888887E-3</v>
       </c>
-      <c r="I37" s="8">
+      <c r="J37" s="8">
         <v>8.1686317729999995</v>
       </c>
-      <c r="J37" s="4">
+      <c r="K37" s="4">
         <f t="shared" si="3"/>
         <v>8168.6317729999992</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="8">
         <v>100</v>
       </c>
-      <c r="D38" s="8">
+      <c r="E38" s="8">
         <v>114</v>
       </c>
-      <c r="E38" s="8">
-        <v>3</v>
-      </c>
-      <c r="F38" s="5">
+      <c r="F38" s="8">
+        <v>3</v>
+      </c>
+      <c r="G38" s="5">
         <f t="shared" si="4"/>
         <v>9.1608841778678361E-3</v>
       </c>
-      <c r="G38" s="5">
+      <c r="H38" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
+        <v>3.0322158034578446E-2</v>
+      </c>
+      <c r="I38" s="5">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="8">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1</v>
+      </c>
+      <c r="K38" s="4">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="8">
         <v>125</v>
       </c>
-      <c r="D39" s="8">
+      <c r="E39" s="8">
         <v>141</v>
       </c>
-      <c r="E39" s="8">
-        <v>3</v>
-      </c>
-      <c r="F39" s="5">
+      <c r="F39" s="8">
+        <v>3</v>
+      </c>
+      <c r="G39" s="5">
         <f t="shared" si="4"/>
         <v>1.4313881527918496E-2</v>
       </c>
-      <c r="G39" s="5">
+      <c r="H39" s="5">
         <f t="shared" si="5"/>
         <v>1.9763665296470374</v>
       </c>
-      <c r="H39" s="5">
+      <c r="I39" s="5">
         <f t="shared" si="6"/>
         <v>2.8289476361111111E-2</v>
       </c>
-      <c r="I39" s="8">
+      <c r="J39" s="8">
         <v>101.8421149</v>
       </c>
-      <c r="J39" s="4">
+      <c r="K39" s="4">
         <f t="shared" si="3"/>
         <v>101842.1149</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="8">
         <v>200</v>
       </c>
-      <c r="D40" s="8">
+      <c r="E40" s="8">
         <v>220</v>
       </c>
-      <c r="E40" s="8">
-        <v>3</v>
-      </c>
-      <c r="F40" s="5">
+      <c r="F40" s="8">
+        <v>3</v>
+      </c>
+      <c r="G40" s="5">
         <f t="shared" si="4"/>
         <v>3.5968094290949541E-2</v>
       </c>
-      <c r="G40" s="5">
+      <c r="H40" s="5">
         <f t="shared" si="5"/>
         <v>0.21624103058845845</v>
       </c>
-      <c r="H40" s="5">
+      <c r="I40" s="5">
         <f t="shared" si="6"/>
         <v>7.7777777777777776E-3</v>
       </c>
-      <c r="I40" s="8">
+      <c r="J40" s="8">
         <v>28</v>
       </c>
-      <c r="J40" s="4">
+      <c r="K40" s="4">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="8">
         <v>80</v>
       </c>
-      <c r="D41" s="8">
+      <c r="E41" s="8">
         <v>88.9</v>
       </c>
-      <c r="E41" s="8">
-        <v>3</v>
-      </c>
-      <c r="F41" s="5">
+      <c r="F41" s="8">
+        <v>3</v>
+      </c>
+      <c r="G41" s="5">
         <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G41" s="5">
+      <c r="H41" s="5">
         <f t="shared" si="5"/>
         <v>4.0967727478173011</v>
       </c>
-      <c r="H41" s="5">
+      <c r="I41" s="5">
         <f t="shared" si="6"/>
         <v>2.2112651241666666E-2</v>
       </c>
-      <c r="I41" s="8">
+      <c r="J41" s="8">
         <v>79.605544469999998</v>
       </c>
-      <c r="J41" s="4">
+      <c r="K41" s="4">
         <f t="shared" si="3"/>
         <v>79605.544469999993</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="8">
         <v>80</v>
       </c>
-      <c r="D42" s="8">
+      <c r="E42" s="8">
         <v>88.9</v>
       </c>
-      <c r="E42" s="8">
-        <v>3</v>
-      </c>
-      <c r="F42" s="5">
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
+      <c r="G42" s="5">
         <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G42" s="5">
+      <c r="H42" s="5">
         <f t="shared" si="5"/>
         <v>1.1443697333909624</v>
       </c>
-      <c r="H42" s="5">
+      <c r="I42" s="5">
         <f t="shared" si="6"/>
         <v>6.1768251166666663E-3</v>
       </c>
-      <c r="I42" s="8">
+      <c r="J42" s="8">
         <v>22.23657042</v>
       </c>
-      <c r="J42" s="4">
+      <c r="K42" s="4">
         <f t="shared" si="3"/>
         <v>22236.57042</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="8">
         <v>50</v>
       </c>
-      <c r="D43" s="8">
+      <c r="E43" s="8">
         <v>60.3</v>
       </c>
-      <c r="E43" s="8">
-        <v>3</v>
-      </c>
-      <c r="F43" s="5">
+      <c r="F43" s="8">
+        <v>3</v>
+      </c>
+      <c r="G43" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G43" s="5">
+      <c r="H43" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H43" s="5">
+      <c r="I43" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I43" s="8">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="8">
         <v>50</v>
       </c>
-      <c r="D44" s="8">
+      <c r="E44" s="8">
         <v>60.3</v>
       </c>
-      <c r="E44" s="8">
-        <v>3</v>
-      </c>
-      <c r="F44" s="5">
+      <c r="F44" s="8">
+        <v>3</v>
+      </c>
+      <c r="G44" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G44" s="5">
+      <c r="H44" s="5">
         <f t="shared" si="5"/>
         <v>3.3847969636442454</v>
       </c>
-      <c r="H44" s="5">
+      <c r="I44" s="5">
         <f t="shared" si="6"/>
         <v>7.8383050861111116E-3</v>
       </c>
-      <c r="I44" s="8">
+      <c r="J44" s="8">
         <v>28.217898309999999</v>
       </c>
-      <c r="J44" s="4">
+      <c r="K44" s="4">
         <f t="shared" si="3"/>
         <v>28217.89831</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="8">
         <v>65</v>
       </c>
-      <c r="D45" s="8">
+      <c r="E45" s="8">
         <v>76.099999999999994</v>
       </c>
-      <c r="E45" s="8">
-        <v>3</v>
-      </c>
-      <c r="F45" s="5">
+      <c r="F45" s="8">
+        <v>3</v>
+      </c>
+      <c r="G45" s="5">
         <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
-      <c r="G45" s="5">
+      <c r="H45" s="5">
         <f t="shared" si="5"/>
         <v>1.1041906103974501</v>
       </c>
-      <c r="H45" s="5">
+      <c r="I45" s="5">
         <f t="shared" si="6"/>
         <v>4.2615733416666666E-3</v>
       </c>
-      <c r="I45" s="8">
+      <c r="J45" s="8">
         <v>15.34166403</v>
       </c>
-      <c r="J45" s="4">
+      <c r="K45" s="4">
         <f t="shared" si="3"/>
         <v>15341.66403</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="8">
         <v>65</v>
       </c>
-      <c r="D46" s="8">
+      <c r="E46" s="8">
         <v>76.099999999999994</v>
       </c>
-      <c r="E46" s="8">
-        <v>3</v>
-      </c>
-      <c r="F46" s="5">
+      <c r="F46" s="8">
+        <v>3</v>
+      </c>
+      <c r="G46" s="5">
         <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
-      <c r="G46" s="5">
+      <c r="H46" s="5">
         <f t="shared" si="5"/>
         <v>1.0003778179300111</v>
       </c>
-      <c r="H46" s="5">
+      <c r="I46" s="5">
         <f t="shared" si="6"/>
         <v>3.8609126E-3</v>
       </c>
-      <c r="I46" s="8">
+      <c r="J46" s="8">
         <v>13.89928536</v>
       </c>
-      <c r="J46" s="4">
+      <c r="K46" s="4">
         <f t="shared" si="3"/>
         <v>13899.28536</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="8">
         <v>50</v>
       </c>
-      <c r="D47" s="8">
+      <c r="E47" s="8">
         <v>60.3</v>
       </c>
-      <c r="E47" s="8">
-        <v>3</v>
-      </c>
-      <c r="F47" s="5">
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
+      <c r="G47" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G47" s="5">
+      <c r="H47" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H47" s="5">
+      <c r="I47" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I47" s="8">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="8">
         <v>50</v>
       </c>
-      <c r="D48" s="8">
+      <c r="E48" s="8">
         <v>60.3</v>
       </c>
-      <c r="E48" s="8">
-        <v>3</v>
-      </c>
-      <c r="F48" s="5">
+      <c r="F48" s="8">
+        <v>3</v>
+      </c>
+      <c r="G48" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G48" s="5">
+      <c r="H48" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H48" s="5">
+      <c r="I48" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I48" s="8">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J48" s="8">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="8">
         <v>32</v>
       </c>
-      <c r="D49" s="8">
+      <c r="E49" s="8">
         <v>42.2</v>
       </c>
-      <c r="E49" s="8">
-        <v>3</v>
-      </c>
-      <c r="F49" s="5">
+      <c r="F49" s="8">
+        <v>3</v>
+      </c>
+      <c r="G49" s="5">
         <f t="shared" si="4"/>
         <v>1.0292171692425523E-3</v>
       </c>
-      <c r="G49" s="5">
+      <c r="H49" s="5">
         <f t="shared" si="5"/>
         <v>0.31745062740409141</v>
       </c>
-      <c r="H49" s="5">
+      <c r="I49" s="5">
         <f t="shared" si="6"/>
         <v>3.2672563611111115E-4</v>
       </c>
-      <c r="I49" s="8">
+      <c r="J49" s="8">
         <v>1.17621229</v>
       </c>
-      <c r="J49" s="4">
+      <c r="K49" s="4">
         <f t="shared" si="3"/>
         <v>1176.2122899999999</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="8">
         <v>80</v>
       </c>
-      <c r="D50" s="8">
+      <c r="E50" s="8">
         <v>88.9</v>
       </c>
-      <c r="E50" s="8">
-        <v>3</v>
-      </c>
-      <c r="F50" s="5">
+      <c r="F50" s="8">
+        <v>3</v>
+      </c>
+      <c r="G50" s="5">
         <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G50" s="5">
+      <c r="H50" s="5">
         <f t="shared" si="5"/>
         <v>0.52441647116270518</v>
       </c>
-      <c r="H50" s="5">
+      <c r="I50" s="5">
         <f t="shared" si="6"/>
         <v>2.8305789083333333E-3</v>
       </c>
-      <c r="I50" s="8">
+      <c r="J50" s="8">
         <v>10.190084069999999</v>
       </c>
-      <c r="J50" s="4">
+      <c r="K50" s="4">
         <f t="shared" si="3"/>
         <v>10190.084069999999</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" s="8">
         <v>125</v>
       </c>
-      <c r="D51" s="8">
+      <c r="E51" s="8">
         <v>139.69999999999999</v>
       </c>
-      <c r="E51" s="8">
-        <v>3</v>
-      </c>
-      <c r="F51" s="5">
+      <c r="F51" s="8">
+        <v>3</v>
+      </c>
+      <c r="G51" s="5">
         <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
-      <c r="G51" s="5">
+      <c r="H51" s="5">
         <f t="shared" si="5"/>
         <v>0.64898914116708672</v>
       </c>
-      <c r="H51" s="5">
+      <c r="I51" s="5">
         <f t="shared" si="6"/>
         <v>9.1115051749999995E-3</v>
       </c>
-      <c r="I51" s="8">
+      <c r="J51" s="8">
         <v>32.801418630000001</v>
       </c>
-      <c r="J51" s="4">
+      <c r="K51" s="4">
         <f t="shared" si="3"/>
         <v>32801.41863</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="8">
         <v>50</v>
       </c>
-      <c r="D52" s="8">
+      <c r="E52" s="8">
         <v>60.3</v>
       </c>
-      <c r="E52" s="8">
-        <v>3</v>
-      </c>
-      <c r="F52" s="5">
+      <c r="F52" s="8">
+        <v>3</v>
+      </c>
+      <c r="G52" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G52" s="5">
+      <c r="H52" s="5">
         <f t="shared" si="5"/>
         <v>1.2982213603797359</v>
       </c>
-      <c r="H52" s="5">
+      <c r="I52" s="5">
         <f t="shared" si="6"/>
         <v>3.0063413555555555E-3</v>
       </c>
-      <c r="I52" s="8">
+      <c r="J52" s="8">
         <v>10.822828879999999</v>
       </c>
-      <c r="J52" s="4">
+      <c r="K52" s="4">
         <f t="shared" si="3"/>
         <v>10822.828879999999</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="8">
         <v>50</v>
       </c>
-      <c r="D53" s="8">
+      <c r="E53" s="8">
         <v>60.3</v>
       </c>
-      <c r="E53" s="8">
-        <v>3</v>
-      </c>
-      <c r="F53" s="5">
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="G53" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G53" s="5">
+      <c r="H53" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H53" s="5">
+      <c r="I53" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I53" s="8">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="8">
-        <v>43</v>
+      <c r="C54" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D54" s="8">
         <v>43</v>
       </c>
       <c r="E54" s="8">
-        <v>3</v>
-      </c>
-      <c r="F54" s="5">
+        <v>43</v>
+      </c>
+      <c r="F54" s="8">
+        <v>3</v>
+      </c>
+      <c r="G54" s="5">
         <f t="shared" si="4"/>
         <v>1.0752100856911066E-3</v>
       </c>
-      <c r="G54" s="5">
+      <c r="H54" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H54" s="5">
+      <c r="I54" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J54" s="8"/>
+      <c r="K54" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="8">
         <v>40</v>
       </c>
-      <c r="D55" s="8">
+      <c r="E55" s="8">
         <v>48.3</v>
       </c>
-      <c r="E55" s="8">
-        <v>3</v>
-      </c>
-      <c r="F55" s="5">
+      <c r="F55" s="8">
+        <v>3</v>
+      </c>
+      <c r="G55" s="5">
         <f t="shared" si="4"/>
         <v>1.4053050797854202E-3</v>
       </c>
-      <c r="G55" s="5">
+      <c r="H55" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H55" s="5">
+      <c r="I55" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J55" s="8"/>
+      <c r="K55" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="8">
         <v>100</v>
       </c>
-      <c r="D56" s="8">
+      <c r="E56" s="8">
         <v>114</v>
       </c>
-      <c r="E56" s="8">
-        <v>3</v>
-      </c>
-      <c r="F56" s="5">
+      <c r="F56" s="8">
+        <v>3</v>
+      </c>
+      <c r="G56" s="5">
         <f t="shared" si="4"/>
         <v>9.1608841778678361E-3</v>
       </c>
-      <c r="G56" s="5">
+      <c r="H56" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H56" s="5">
+      <c r="I56" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I56" s="8"/>
-      <c r="J56" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J56" s="8"/>
+      <c r="K56" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="8">
         <v>50</v>
       </c>
-      <c r="D57" s="8">
+      <c r="E57" s="8">
         <v>60.3</v>
       </c>
-      <c r="E57" s="8">
-        <v>3</v>
-      </c>
-      <c r="F57" s="5">
+      <c r="F57" s="8">
+        <v>3</v>
+      </c>
+      <c r="G57" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G57" s="5">
+      <c r="H57" s="5">
         <f t="shared" si="5"/>
         <v>0.97984476797762998</v>
       </c>
-      <c r="H57" s="5">
+      <c r="I57" s="5">
         <f t="shared" si="6"/>
         <v>2.2690643813888887E-3</v>
       </c>
-      <c r="I57" s="8">
+      <c r="J57" s="8">
         <v>8.1686317729999995</v>
       </c>
-      <c r="J57" s="4">
+      <c r="K57" s="4">
         <f t="shared" si="3"/>
         <v>8168.6317729999992</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="8">
         <v>80</v>
       </c>
-      <c r="D58" s="8">
+      <c r="E58" s="8">
         <v>88.9</v>
       </c>
-      <c r="E58" s="8">
-        <v>3</v>
-      </c>
-      <c r="F58" s="5">
+      <c r="F58" s="8">
+        <v>3</v>
+      </c>
+      <c r="G58" s="5">
         <f t="shared" si="4"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G58" s="5">
+      <c r="H58" s="5">
         <f t="shared" si="5"/>
         <v>5.1463409679475318E-2</v>
       </c>
-      <c r="H58" s="5">
+      <c r="I58" s="5">
         <f t="shared" si="6"/>
         <v>2.7777777777777778E-4</v>
       </c>
-      <c r="I58" s="8">
+      <c r="J58" s="8">
         <v>1</v>
       </c>
-      <c r="J58" s="4">
+      <c r="K58" s="4">
         <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="8">
         <v>50</v>
       </c>
-      <c r="D59" s="8">
+      <c r="E59" s="8">
         <v>60.3</v>
       </c>
-      <c r="E59" s="8">
-        <v>3</v>
-      </c>
-      <c r="F59" s="5">
+      <c r="F59" s="8">
+        <v>3</v>
+      </c>
+      <c r="G59" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G59" s="5">
+      <c r="H59" s="5">
         <f t="shared" si="5"/>
         <v>0.11995212848452021</v>
       </c>
-      <c r="H59" s="5">
+      <c r="I59" s="5">
         <f t="shared" si="6"/>
         <v>2.7777777777777778E-4</v>
       </c>
-      <c r="I59" s="8">
+      <c r="J59" s="8">
         <v>1</v>
       </c>
-      <c r="J59" s="4">
+      <c r="K59" s="4">
         <f t="shared" si="3"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="8">
         <v>50</v>
       </c>
-      <c r="D60" s="8">
+      <c r="E60" s="8">
         <v>60.3</v>
       </c>
-      <c r="E60" s="8">
-        <v>3</v>
-      </c>
-      <c r="F60" s="5">
+      <c r="F60" s="8">
+        <v>3</v>
+      </c>
+      <c r="G60" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G60" s="5">
+      <c r="H60" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H60" s="5">
+      <c r="I60" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J60" s="8"/>
+      <c r="K60" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" s="8">
         <v>50</v>
       </c>
-      <c r="D61" s="8">
+      <c r="E61" s="8">
         <v>60.3</v>
       </c>
-      <c r="E61" s="8">
-        <v>3</v>
-      </c>
-      <c r="F61" s="5">
+      <c r="F61" s="8">
+        <v>3</v>
+      </c>
+      <c r="G61" s="5">
         <f t="shared" si="4"/>
         <v>2.3157386307957424E-3</v>
       </c>
-      <c r="G61" s="5">
+      <c r="H61" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H61" s="5">
+      <c r="I61" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I61" s="8"/>
-      <c r="J61" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J61" s="8"/>
+      <c r="K61" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C62" s="8">
-        <v>73</v>
+      <c r="C62" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D62" s="8">
         <v>73</v>
       </c>
       <c r="E62" s="8">
-        <v>3</v>
-      </c>
-      <c r="F62" s="5">
+        <v>73</v>
+      </c>
+      <c r="F62" s="8">
+        <v>3</v>
+      </c>
+      <c r="G62" s="5">
         <f t="shared" si="4"/>
         <v>3.5256523554911458E-3</v>
       </c>
-      <c r="G62" s="5">
+      <c r="H62" s="5">
         <f t="shared" si="5"/>
         <v>1.3500000001822385</v>
       </c>
-      <c r="H62" s="5">
+      <c r="I62" s="5">
         <f t="shared" si="6"/>
         <v>4.7596306805555563E-3</v>
       </c>
-      <c r="I62" s="8">
+      <c r="J62" s="8">
         <v>17.134670450000002</v>
       </c>
-      <c r="J62" s="4">
+      <c r="K62" s="4">
         <f t="shared" si="3"/>
         <v>17134.670450000001</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="8">
         <v>65</v>
       </c>
-      <c r="D63" s="8">
+      <c r="E63" s="8">
         <v>76.099999999999994</v>
       </c>
-      <c r="E63" s="8">
-        <v>3</v>
-      </c>
-      <c r="F63" s="5">
+      <c r="F63" s="8">
+        <v>3</v>
+      </c>
+      <c r="G63" s="5">
         <f t="shared" si="4"/>
         <v>3.8594544289166943E-3</v>
       </c>
-      <c r="G63" s="5">
+      <c r="H63" s="5">
         <f t="shared" si="5"/>
         <v>1.8267449193391221</v>
       </c>
-      <c r="H63" s="5">
+      <c r="I63" s="5">
         <f t="shared" si="6"/>
         <v>7.0502387694444443E-3</v>
       </c>
-      <c r="I63" s="8">
+      <c r="J63" s="8">
         <v>25.380859569999998</v>
       </c>
-      <c r="J63" s="4">
+      <c r="K63" s="4">
         <f t="shared" si="3"/>
         <v>25380.859569999997</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="8">
         <v>125</v>
       </c>
-      <c r="D64" s="8">
+      <c r="E64" s="8">
         <v>139.69999999999999</v>
       </c>
-      <c r="E64" s="8">
-        <v>3</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="F64" s="8">
+        <v>3</v>
+      </c>
+      <c r="G64" s="5">
         <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
-      <c r="G64" s="5">
+      <c r="H64" s="5">
         <f t="shared" si="5"/>
         <v>2.9678097850935239</v>
       </c>
-      <c r="H64" s="5">
+      <c r="I64" s="5">
         <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I64" s="8">
+      <c r="J64" s="8">
         <v>150</v>
       </c>
-      <c r="J64" s="4">
+      <c r="K64" s="4">
         <f t="shared" si="3"/>
         <v>150000</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="8">
         <v>125</v>
       </c>
-      <c r="D65" s="8">
+      <c r="E65" s="8">
         <v>139.69999999999999</v>
       </c>
-      <c r="E65" s="8">
-        <v>3</v>
-      </c>
-      <c r="F65" s="5">
+      <c r="F65" s="8">
+        <v>3</v>
+      </c>
+      <c r="G65" s="5">
         <f t="shared" si="4"/>
         <v>1.4039534095462129E-2</v>
       </c>
-      <c r="G65" s="5">
+      <c r="H65" s="5">
         <f t="shared" si="5"/>
         <v>0.8705575369607671</v>
       </c>
-      <c r="H65" s="5">
+      <c r="I65" s="5">
         <f t="shared" si="6"/>
         <v>1.2222222222222223E-2</v>
       </c>
-      <c r="I65" s="8">
+      <c r="J65" s="8">
         <v>44</v>
       </c>
-      <c r="J65" s="4">
+      <c r="K65" s="4">
         <f t="shared" si="3"/>
         <v>44000</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="8">
         <v>80</v>
       </c>
-      <c r="D66" s="8">
+      <c r="E66" s="8">
         <v>88.9</v>
       </c>
-      <c r="E66" s="8">
-        <v>3</v>
-      </c>
-      <c r="F66" s="5">
-        <f t="shared" ref="F66:F72" si="7">(PI()/4)*((D66-2*E66)*10^-3)^2</f>
+      <c r="F66" s="8">
+        <v>3</v>
+      </c>
+      <c r="G66" s="5">
+        <f t="shared" ref="G66:G72" si="7">(PI()/4)*((E66-2*F66)*10^-3)^2</f>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G66" s="5">
-        <f t="shared" ref="G66:G97" si="8">H66/F66</f>
+      <c r="H66" s="5">
+        <f t="shared" ref="H66:H72" si="8">I66/G66</f>
         <v>2.4187802549353399</v>
       </c>
-      <c r="H66" s="5">
-        <f t="shared" ref="H66:H97" si="9">I66/3600</f>
+      <c r="I66" s="5">
+        <f t="shared" ref="I66:I72" si="9">J66/3600</f>
         <v>1.3055555555555556E-2</v>
       </c>
-      <c r="I66" s="8">
+      <c r="J66" s="8">
         <v>47</v>
       </c>
-      <c r="J66" s="4">
+      <c r="K66" s="4">
         <f t="shared" si="3"/>
         <v>47000</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" s="8">
         <v>80</v>
       </c>
-      <c r="D67" s="8">
+      <c r="E67" s="8">
         <v>88.9</v>
       </c>
-      <c r="E67" s="8">
-        <v>3</v>
-      </c>
-      <c r="F67" s="5">
+      <c r="F67" s="8">
+        <v>3</v>
+      </c>
+      <c r="G67" s="5">
         <f t="shared" si="7"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G67" s="5">
+      <c r="H67" s="5">
         <f t="shared" si="8"/>
         <v>3.4480484485248462</v>
       </c>
-      <c r="H67" s="5">
+      <c r="I67" s="5">
         <f t="shared" si="9"/>
         <v>1.861111111111111E-2</v>
       </c>
-      <c r="I67" s="8">
+      <c r="J67" s="8">
         <v>67</v>
       </c>
-      <c r="J67" s="4">
-        <f t="shared" ref="J67:J72" si="10">I67*1000</f>
+      <c r="K67" s="4">
+        <f t="shared" ref="K67:K72" si="10">J67*1000</f>
         <v>67000</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="8">
         <v>80</v>
       </c>
-      <c r="D68" s="8">
+      <c r="E68" s="8">
         <v>88.9</v>
       </c>
-      <c r="E68" s="8">
-        <v>3</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="F68" s="8">
+        <v>3</v>
+      </c>
+      <c r="G68" s="5">
         <f t="shared" si="7"/>
         <v>5.3975781921142578E-3</v>
       </c>
-      <c r="G68" s="5">
+      <c r="H68" s="5">
         <f t="shared" si="8"/>
-        <v>0.2270819116024291</v>
-      </c>
-      <c r="H68" s="5">
+        <v>1.2093901274676699</v>
+      </c>
+      <c r="I68" s="5">
         <f t="shared" si="9"/>
-        <v>1.225692373888889E-3</v>
-      </c>
-      <c r="I68" s="8">
-        <v>4.4124925460000002</v>
-      </c>
-      <c r="J68" s="4">
+        <v>6.5277777777777782E-3</v>
+      </c>
+      <c r="J68" s="8">
+        <f>41-17.5</f>
+        <v>23.5</v>
+      </c>
+      <c r="K68" s="4">
         <f t="shared" si="10"/>
-        <v>4412.4925460000004</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="8">
         <v>65</v>
       </c>
-      <c r="D69" s="8">
+      <c r="E69" s="8">
         <v>76.099999999999994</v>
       </c>
-      <c r="E69" s="8">
-        <v>3</v>
-      </c>
-      <c r="F69" s="5">
+      <c r="F69" s="8">
+        <v>3</v>
+      </c>
+      <c r="G69" s="5">
         <f t="shared" si="7"/>
         <v>3.8594544289166943E-3</v>
       </c>
-      <c r="G69" s="5">
+      <c r="H69" s="5">
         <f t="shared" si="8"/>
-        <v>0.89981501849423517</v>
-      </c>
-      <c r="H69" s="5">
+        <v>1.259533232129799</v>
+      </c>
+      <c r="I69" s="5">
         <f t="shared" si="9"/>
-        <v>3.4727950583333333E-3</v>
-      </c>
-      <c r="I69" s="8">
-        <v>12.50206221</v>
-      </c>
-      <c r="J69" s="4">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="J69" s="8">
+        <v>17.5</v>
+      </c>
+      <c r="K69" s="4">
         <f t="shared" si="10"/>
-        <v>12502.06221</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="8">
-        <v>129</v>
+      <c r="C70" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D70" s="8">
         <v>129</v>
       </c>
       <c r="E70" s="8">
-        <v>3</v>
-      </c>
-      <c r="F70" s="5">
+        <v>129</v>
+      </c>
+      <c r="F70" s="8">
+        <v>3</v>
+      </c>
+      <c r="G70" s="5">
         <f t="shared" si="7"/>
         <v>1.1882288814039995E-2</v>
       </c>
-      <c r="G70" s="5">
+      <c r="H70" s="5">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H70" s="5">
+      <c r="I70" s="5">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I70" s="8">
-        <v>0</v>
-      </c>
-      <c r="J70" s="4">
+      <c r="J70" s="8">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C71" s="8">
-        <v>129</v>
+      <c r="C71" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D71" s="8">
         <v>129</v>
       </c>
       <c r="E71" s="8">
-        <v>3</v>
-      </c>
-      <c r="F71" s="5">
+        <v>129</v>
+      </c>
+      <c r="F71" s="8">
+        <v>3</v>
+      </c>
+      <c r="G71" s="5">
         <f t="shared" si="7"/>
         <v>1.1882288814039995E-2</v>
       </c>
-      <c r="G71" s="5">
+      <c r="H71" s="5">
         <f t="shared" si="8"/>
         <v>1.7533097923622991</v>
       </c>
-      <c r="H71" s="5">
+      <c r="I71" s="5">
         <f t="shared" si="9"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="I71" s="8">
+      <c r="J71" s="8">
         <v>75</v>
       </c>
-      <c r="J71" s="4">
+      <c r="K71" s="4">
         <f t="shared" si="10"/>
         <v>75000</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" s="8">
         <v>100</v>
       </c>
-      <c r="D72" s="8">
+      <c r="E72" s="8">
         <v>114</v>
       </c>
-      <c r="E72" s="8">
-        <v>3</v>
-      </c>
-      <c r="F72" s="5">
+      <c r="F72" s="8">
+        <v>3</v>
+      </c>
+      <c r="G72" s="5">
         <f t="shared" si="7"/>
         <v>9.1608841778678361E-3</v>
       </c>
-      <c r="G72" s="5">
+      <c r="H72" s="5">
         <f t="shared" si="8"/>
         <v>2.1831953784896481</v>
       </c>
-      <c r="H72" s="5">
+      <c r="I72" s="5">
         <f t="shared" si="9"/>
         <v>0.02</v>
       </c>
-      <c r="I72" s="8">
+      <c r="J72" s="8">
         <v>72</v>
       </c>
-      <c r="J72" s="4">
+      <c r="K72" s="4">
         <f t="shared" si="10"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="10"/>
+      <c r="C73" s="1"/>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
-      <c r="I73" s="10"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F73" s="10"/>
+      <c r="J73" s="10"/>
+    </row>
+    <row r="74" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="10"/>
+      <c r="C74" s="1"/>
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
-      <c r="I74" s="10"/>
-    </row>
-    <row r="75" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F74" s="10"/>
+      <c r="J74" s="10"/>
+    </row>
+    <row r="75" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="10"/>
+      <c r="C75" s="1"/>
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
-      <c r="I75" s="10"/>
-    </row>
-    <row r="76" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F75" s="10"/>
+      <c r="J75" s="10"/>
+    </row>
+    <row r="76" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="10"/>
+      <c r="C76" s="1"/>
       <c r="D76" s="10"/>
       <c r="E76" s="10"/>
-      <c r="I76" s="10"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F76" s="10"/>
+      <c r="J76" s="10"/>
+    </row>
+    <row r="77" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="10"/>
+      <c r="C77" s="1"/>
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
-      <c r="I77" s="10"/>
-    </row>
-    <row r="78" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F77" s="10"/>
+      <c r="J77" s="10"/>
+    </row>
+    <row r="78" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="10"/>
+      <c r="C78" s="1"/>
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
-      <c r="I78" s="10"/>
-    </row>
-    <row r="79" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F78" s="10"/>
+      <c r="J78" s="10"/>
+    </row>
+    <row r="79" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="10"/>
+      <c r="C79" s="1"/>
       <c r="D79" s="10"/>
       <c r="E79" s="10"/>
-      <c r="I79" s="10"/>
-    </row>
-    <row r="80" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F79" s="10"/>
+      <c r="J79" s="10"/>
+    </row>
+    <row r="80" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
-      <c r="C80" s="10"/>
+      <c r="C80" s="1"/>
       <c r="D80" s="10"/>
       <c r="E80" s="10"/>
-      <c r="I80" s="10"/>
-    </row>
-    <row r="81" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F80" s="10"/>
+      <c r="J80" s="10"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
-      <c r="C81" s="10"/>
+      <c r="C81" s="1"/>
       <c r="D81" s="10"/>
       <c r="E81" s="10"/>
-      <c r="I81" s="10"/>
-    </row>
-    <row r="82" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F81" s="10"/>
+      <c r="J81" s="10"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
-      <c r="C82" s="10"/>
+      <c r="C82" s="1"/>
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
-      <c r="I82" s="10"/>
-    </row>
-    <row r="83" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F82" s="10"/>
+      <c r="J82" s="10"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
-      <c r="C83" s="10"/>
+      <c r="C83" s="1"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
-      <c r="I83" s="10"/>
-    </row>
-    <row r="84" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F83" s="10"/>
+      <c r="J83" s="10"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
-      <c r="C84" s="10"/>
+      <c r="C84" s="1"/>
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
-      <c r="I84" s="10"/>
-    </row>
-    <row r="85" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F84" s="10"/>
+      <c r="J84" s="10"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
-      <c r="C85" s="10"/>
+      <c r="C85" s="1"/>
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
-      <c r="I85" s="10"/>
-    </row>
-    <row r="86" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F85" s="10"/>
+      <c r="J85" s="10"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
-      <c r="C86" s="10"/>
+      <c r="C86" s="1"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
-      <c r="I86" s="10"/>
-    </row>
-    <row r="87" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F86" s="10"/>
+      <c r="J86" s="10"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
-      <c r="C87" s="10"/>
+      <c r="C87" s="1"/>
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
-      <c r="I87" s="10"/>
-    </row>
-    <row r="88" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F87" s="10"/>
+      <c r="J87" s="10"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="10"/>
+      <c r="C88" s="1"/>
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
-      <c r="I88" s="10"/>
-    </row>
-    <row r="89" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F88" s="10"/>
+      <c r="J88" s="10"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="10"/>
+      <c r="C89" s="1"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
-      <c r="I89" s="10"/>
-    </row>
-    <row r="90" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F89" s="10"/>
+      <c r="J89" s="10"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
-      <c r="C90" s="10"/>
+      <c r="C90" s="1"/>
       <c r="D90" s="10"/>
       <c r="E90" s="10"/>
-      <c r="I90" s="10"/>
-    </row>
-    <row r="91" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F90" s="10"/>
+      <c r="J90" s="10"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-      <c r="C91" s="10"/>
+      <c r="C91" s="1"/>
       <c r="D91" s="10"/>
       <c r="E91" s="10"/>
-      <c r="I91" s="10"/>
-    </row>
-    <row r="92" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F91" s="10"/>
+      <c r="J91" s="10"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
-      <c r="C92" s="10"/>
+      <c r="C92" s="1"/>
       <c r="D92" s="10"/>
       <c r="E92" s="10"/>
-      <c r="I92" s="10"/>
-    </row>
-    <row r="93" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F92" s="10"/>
+      <c r="J92" s="10"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="10"/>
+      <c r="C93" s="1"/>
       <c r="D93" s="10"/>
       <c r="E93" s="10"/>
-      <c r="I93" s="10"/>
-    </row>
-    <row r="94" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F93" s="10"/>
+      <c r="J93" s="10"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
-      <c r="C94" s="10"/>
+      <c r="C94" s="1"/>
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
-      <c r="I94" s="10"/>
-    </row>
-    <row r="95" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F94" s="10"/>
+      <c r="J94" s="10"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
-      <c r="C95" s="10"/>
+      <c r="C95" s="1"/>
       <c r="D95" s="10"/>
       <c r="E95" s="10"/>
-      <c r="I95" s="10"/>
-    </row>
-    <row r="96" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F95" s="10"/>
+      <c r="J95" s="10"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
-      <c r="C96" s="10"/>
+      <c r="C96" s="1"/>
       <c r="D96" s="10"/>
       <c r="E96" s="10"/>
-      <c r="I96" s="10"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F96" s="10"/>
+      <c r="J96" s="10"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
-      <c r="C97" s="10"/>
+      <c r="C97" s="1"/>
       <c r="D97" s="10"/>
       <c r="E97" s="10"/>
-      <c r="I97" s="10"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F97" s="10"/>
+      <c r="J97" s="10"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
-      <c r="C98" s="10"/>
+      <c r="C98" s="1"/>
       <c r="D98" s="10"/>
       <c r="E98" s="10"/>
-      <c r="I98" s="10"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F98" s="10"/>
+      <c r="J98" s="10"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
-      <c r="C99" s="10"/>
+      <c r="C99" s="1"/>
       <c r="D99" s="10"/>
       <c r="E99" s="10"/>
-      <c r="I99" s="10"/>
-    </row>
-    <row r="100" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F99" s="10"/>
+      <c r="J99" s="10"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
-      <c r="C100" s="10"/>
+      <c r="C100" s="1"/>
       <c r="D100" s="10"/>
       <c r="E100" s="10"/>
-      <c r="I100" s="10"/>
-    </row>
-    <row r="101" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F100" s="10"/>
+      <c r="J100" s="10"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
-      <c r="C101" s="10"/>
+      <c r="C101" s="1"/>
       <c r="D101" s="10"/>
       <c r="E101" s="10"/>
-      <c r="I101" s="10"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F101" s="10"/>
+      <c r="J101" s="10"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
-      <c r="C102" s="10"/>
+      <c r="C102" s="1"/>
       <c r="D102" s="10"/>
       <c r="E102" s="10"/>
-      <c r="I102" s="10"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F102" s="10"/>
+      <c r="J102" s="10"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="C103" s="10"/>
+      <c r="C103" s="1"/>
       <c r="D103" s="10"/>
       <c r="E103" s="10"/>
-      <c r="I103" s="10"/>
-    </row>
-    <row r="104" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F103" s="10"/>
+      <c r="J103" s="10"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
-      <c r="C104" s="10"/>
+      <c r="C104" s="1"/>
       <c r="D104" s="10"/>
       <c r="E104" s="10"/>
-      <c r="I104" s="10"/>
-    </row>
-    <row r="105" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F104" s="10"/>
+      <c r="J104" s="10"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
-      <c r="C105" s="10"/>
+      <c r="C105" s="1"/>
       <c r="D105" s="10"/>
       <c r="E105" s="10"/>
-      <c r="I105" s="10"/>
-    </row>
-    <row r="106" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F105" s="10"/>
+      <c r="J105" s="10"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
-      <c r="C106" s="10"/>
+      <c r="C106" s="1"/>
       <c r="D106" s="10"/>
       <c r="E106" s="10"/>
-      <c r="I106" s="10"/>
-    </row>
-    <row r="107" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F106" s="10"/>
+      <c r="J106" s="10"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="10"/>
+      <c r="C107" s="1"/>
       <c r="D107" s="10"/>
       <c r="E107" s="10"/>
-      <c r="I107" s="10"/>
-    </row>
-    <row r="108" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F107" s="10"/>
+      <c r="J107" s="10"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
-      <c r="C108" s="10"/>
+      <c r="C108" s="1"/>
       <c r="D108" s="10"/>
       <c r="E108" s="10"/>
-      <c r="I108" s="10"/>
-    </row>
-    <row r="109" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F108" s="10"/>
+      <c r="J108" s="10"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
-      <c r="C109" s="10"/>
+      <c r="C109" s="1"/>
       <c r="D109" s="10"/>
       <c r="E109" s="10"/>
-      <c r="I109" s="10"/>
-    </row>
-    <row r="110" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F109" s="10"/>
+      <c r="J109" s="10"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
-      <c r="C110" s="10"/>
+      <c r="C110" s="1"/>
       <c r="D110" s="10"/>
       <c r="E110" s="10"/>
-      <c r="I110" s="10"/>
-    </row>
-    <row r="111" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F110" s="10"/>
+      <c r="J110" s="10"/>
+    </row>
+    <row r="111" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="10"/>
+      <c r="C111" s="1"/>
       <c r="D111" s="10"/>
       <c r="E111" s="10"/>
-      <c r="I111" s="10"/>
-    </row>
-    <row r="112" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F111" s="10"/>
+      <c r="J111" s="10"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
-      <c r="C112" s="10"/>
+      <c r="C112" s="1"/>
       <c r="D112" s="10"/>
       <c r="E112" s="10"/>
-      <c r="I112" s="10"/>
-    </row>
-    <row r="113" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F112" s="10"/>
+      <c r="J112" s="10"/>
+    </row>
+    <row r="113" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
-      <c r="C113" s="10"/>
+      <c r="C113" s="1"/>
       <c r="D113" s="10"/>
       <c r="E113" s="10"/>
-      <c r="I113" s="10"/>
-    </row>
-    <row r="114" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F113" s="10"/>
+      <c r="J113" s="10"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
-      <c r="C114" s="10"/>
+      <c r="C114" s="1"/>
       <c r="D114" s="10"/>
       <c r="E114" s="10"/>
-      <c r="I114" s="10"/>
-    </row>
-    <row r="115" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F114" s="10"/>
+      <c r="J114" s="10"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
-      <c r="C115" s="10"/>
+      <c r="C115" s="1"/>
       <c r="D115" s="10"/>
       <c r="E115" s="10"/>
-      <c r="I115" s="10"/>
-    </row>
-    <row r="116" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F115" s="10"/>
+      <c r="J115" s="10"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
-      <c r="C116" s="10"/>
+      <c r="C116" s="1"/>
       <c r="D116" s="10"/>
       <c r="E116" s="10"/>
-      <c r="I116" s="10"/>
-    </row>
-    <row r="117" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F116" s="10"/>
+      <c r="J116" s="10"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
-      <c r="C117" s="10"/>
+      <c r="C117" s="1"/>
       <c r="D117" s="10"/>
       <c r="E117" s="10"/>
-      <c r="I117" s="10"/>
-    </row>
-    <row r="118" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F117" s="10"/>
+      <c r="J117" s="10"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
-      <c r="C118" s="10"/>
+      <c r="C118" s="1"/>
       <c r="D118" s="10"/>
       <c r="E118" s="10"/>
-      <c r="I118" s="10"/>
-    </row>
-    <row r="119" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F118" s="10"/>
+      <c r="J118" s="10"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
-      <c r="C119" s="10"/>
+      <c r="C119" s="1"/>
       <c r="D119" s="10"/>
       <c r="E119" s="10"/>
-      <c r="I119" s="10"/>
-    </row>
-    <row r="120" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F119" s="10"/>
+      <c r="J119" s="10"/>
+    </row>
+    <row r="120" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-      <c r="C120" s="10"/>
+      <c r="C120" s="1"/>
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
-      <c r="I120" s="10"/>
-    </row>
-    <row r="121" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F120" s="10"/>
+      <c r="J120" s="10"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="10"/>
+      <c r="C121" s="1"/>
       <c r="D121" s="10"/>
       <c r="E121" s="10"/>
-      <c r="I121" s="10"/>
-    </row>
-    <row r="122" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F121" s="10"/>
+      <c r="J121" s="10"/>
+    </row>
+    <row r="122" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
-      <c r="C122" s="10"/>
+      <c r="C122" s="1"/>
       <c r="D122" s="10"/>
       <c r="E122" s="10"/>
-      <c r="I122" s="10"/>
-    </row>
-    <row r="123" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F122" s="10"/>
+      <c r="J122" s="10"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
-      <c r="C123" s="10"/>
+      <c r="C123" s="1"/>
       <c r="D123" s="10"/>
       <c r="E123" s="10"/>
-      <c r="I123" s="10"/>
-    </row>
-    <row r="124" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F123" s="10"/>
+      <c r="J123" s="10"/>
+    </row>
+    <row r="124" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
-      <c r="C124" s="10"/>
+      <c r="C124" s="1"/>
       <c r="D124" s="10"/>
       <c r="E124" s="10"/>
-      <c r="I124" s="10"/>
-    </row>
-    <row r="125" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F124" s="10"/>
+      <c r="J124" s="10"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="10"/>
+      <c r="C125" s="1"/>
       <c r="D125" s="10"/>
       <c r="E125" s="10"/>
-      <c r="I125" s="10"/>
-    </row>
-    <row r="126" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F125" s="10"/>
+      <c r="J125" s="10"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
-      <c r="C126" s="10"/>
+      <c r="C126" s="1"/>
       <c r="D126" s="10"/>
       <c r="E126" s="10"/>
-      <c r="I126" s="10"/>
-    </row>
-    <row r="127" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F126" s="10"/>
+      <c r="J126" s="10"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
-      <c r="C127" s="10"/>
+      <c r="C127" s="1"/>
       <c r="D127" s="10"/>
       <c r="E127" s="10"/>
-      <c r="I127" s="10"/>
-    </row>
-    <row r="128" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F127" s="10"/>
+      <c r="J127" s="10"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
-      <c r="C128" s="10"/>
+      <c r="C128" s="1"/>
       <c r="D128" s="10"/>
       <c r="E128" s="10"/>
-      <c r="I128" s="10"/>
-    </row>
-    <row r="129" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F128" s="10"/>
+      <c r="J128" s="10"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
-      <c r="C129" s="10"/>
+      <c r="C129" s="1"/>
       <c r="D129" s="10"/>
       <c r="E129" s="10"/>
-      <c r="I129" s="10"/>
-    </row>
-    <row r="130" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F129" s="10"/>
+      <c r="J129" s="10"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
-      <c r="C130" s="10"/>
+      <c r="C130" s="1"/>
       <c r="D130" s="10"/>
       <c r="E130" s="10"/>
-      <c r="I130" s="10"/>
-    </row>
-    <row r="131" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F130" s="10"/>
+      <c r="J130" s="10"/>
+    </row>
+    <row r="131" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
-      <c r="C131" s="10"/>
+      <c r="C131" s="1"/>
       <c r="D131" s="10"/>
       <c r="E131" s="10"/>
-      <c r="I131" s="10"/>
-    </row>
-    <row r="132" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F131" s="10"/>
+      <c r="J131" s="10"/>
+    </row>
+    <row r="132" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
-      <c r="C132" s="10"/>
+      <c r="C132" s="1"/>
       <c r="D132" s="10"/>
       <c r="E132" s="10"/>
-      <c r="I132" s="10"/>
-    </row>
-    <row r="133" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F132" s="10"/>
+      <c r="J132" s="10"/>
+    </row>
+    <row r="133" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
-      <c r="C133" s="10"/>
+      <c r="C133" s="1"/>
       <c r="D133" s="10"/>
       <c r="E133" s="10"/>
-      <c r="I133" s="10"/>
-    </row>
-    <row r="134" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F133" s="10"/>
+      <c r="J133" s="10"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
-      <c r="C134" s="10"/>
+      <c r="C134" s="1"/>
       <c r="D134" s="10"/>
       <c r="E134" s="10"/>
-      <c r="I134" s="10"/>
-    </row>
-    <row r="135" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F134" s="10"/>
+      <c r="J134" s="10"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
-      <c r="C135" s="10"/>
+      <c r="C135" s="1"/>
       <c r="D135" s="10"/>
       <c r="E135" s="10"/>
-      <c r="I135" s="10"/>
-    </row>
-    <row r="136" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F135" s="10"/>
+      <c r="J135" s="10"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
-      <c r="C136" s="10"/>
+      <c r="C136" s="1"/>
       <c r="D136" s="10"/>
       <c r="E136" s="10"/>
-      <c r="I136" s="10"/>
-    </row>
-    <row r="137" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F136" s="10"/>
+      <c r="J136" s="10"/>
+    </row>
+    <row r="137" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="10"/>
+      <c r="C137" s="1"/>
       <c r="D137" s="10"/>
       <c r="E137" s="10"/>
-      <c r="I137" s="10"/>
-    </row>
-    <row r="138" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F137" s="10"/>
+      <c r="J137" s="10"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
-      <c r="C138" s="10"/>
+      <c r="C138" s="1"/>
       <c r="D138" s="10"/>
       <c r="E138" s="10"/>
-      <c r="I138" s="10"/>
-    </row>
-    <row r="139" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F138" s="10"/>
+      <c r="J138" s="10"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
-      <c r="C139" s="10"/>
+      <c r="C139" s="1"/>
       <c r="D139" s="10"/>
       <c r="E139" s="10"/>
-      <c r="I139" s="10"/>
-    </row>
-    <row r="140" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F139" s="10"/>
+      <c r="J139" s="10"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
-      <c r="C140" s="10"/>
+      <c r="C140" s="1"/>
       <c r="D140" s="10"/>
       <c r="E140" s="10"/>
-      <c r="I140" s="10"/>
-    </row>
-    <row r="141" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F140" s="10"/>
+      <c r="J140" s="10"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
-      <c r="C141" s="10"/>
+      <c r="C141" s="1"/>
       <c r="D141" s="10"/>
       <c r="E141" s="10"/>
-      <c r="I141" s="10"/>
-    </row>
-    <row r="142" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F141" s="10"/>
+      <c r="J141" s="10"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
-      <c r="C142" s="10"/>
+      <c r="C142" s="1"/>
       <c r="D142" s="10"/>
       <c r="E142" s="10"/>
-      <c r="I142" s="10"/>
-    </row>
-    <row r="143" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F142" s="10"/>
+      <c r="J142" s="10"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
-      <c r="C143" s="10"/>
+      <c r="C143" s="1"/>
       <c r="D143" s="10"/>
       <c r="E143" s="10"/>
-      <c r="I143" s="10"/>
-    </row>
-    <row r="144" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F143" s="10"/>
+      <c r="J143" s="10"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
-      <c r="C144" s="10"/>
+      <c r="C144" s="1"/>
       <c r="D144" s="10"/>
       <c r="E144" s="10"/>
-      <c r="I144" s="10"/>
-    </row>
-    <row r="145" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F144" s="10"/>
+      <c r="J144" s="10"/>
+    </row>
+    <row r="145" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
-      <c r="C145" s="10"/>
+      <c r="C145" s="1"/>
       <c r="D145" s="10"/>
       <c r="E145" s="10"/>
-      <c r="I145" s="10"/>
-    </row>
-    <row r="146" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F145" s="10"/>
+      <c r="J145" s="10"/>
+    </row>
+    <row r="146" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
-      <c r="C146" s="10"/>
+      <c r="C146" s="1"/>
       <c r="D146" s="10"/>
       <c r="E146" s="10"/>
-      <c r="I146" s="10"/>
-    </row>
-    <row r="147" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F146" s="10"/>
+      <c r="J146" s="10"/>
+    </row>
+    <row r="147" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
-      <c r="C147" s="10"/>
+      <c r="C147" s="1"/>
       <c r="D147" s="10"/>
       <c r="E147" s="10"/>
-      <c r="I147" s="10"/>
-    </row>
-    <row r="148" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F147" s="10"/>
+      <c r="J147" s="10"/>
+    </row>
+    <row r="148" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
-      <c r="C148" s="10"/>
+      <c r="C148" s="1"/>
       <c r="D148" s="10"/>
       <c r="E148" s="10"/>
-      <c r="I148" s="10"/>
-    </row>
-    <row r="149" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F148" s="10"/>
+      <c r="J148" s="10"/>
+    </row>
+    <row r="149" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
-      <c r="C149" s="10"/>
+      <c r="C149" s="1"/>
       <c r="D149" s="10"/>
       <c r="E149" s="10"/>
-      <c r="I149" s="10"/>
-    </row>
-    <row r="150" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F149" s="10"/>
+      <c r="J149" s="10"/>
+    </row>
+    <row r="150" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
-      <c r="C150" s="10"/>
+      <c r="C150" s="1"/>
       <c r="D150" s="10"/>
       <c r="E150" s="10"/>
-      <c r="I150" s="10"/>
-    </row>
-    <row r="151" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F150" s="10"/>
+      <c r="J150" s="10"/>
+    </row>
+    <row r="151" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
-      <c r="C151" s="10"/>
+      <c r="C151" s="1"/>
       <c r="D151" s="10"/>
       <c r="E151" s="10"/>
-      <c r="I151" s="10"/>
-    </row>
-    <row r="152" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F151" s="10"/>
+      <c r="J151" s="10"/>
+    </row>
+    <row r="152" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
-      <c r="C152" s="10"/>
+      <c r="C152" s="1"/>
       <c r="D152" s="10"/>
       <c r="E152" s="10"/>
-      <c r="I152" s="10"/>
-    </row>
-    <row r="153" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F152" s="10"/>
+      <c r="J152" s="10"/>
+    </row>
+    <row r="153" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
-      <c r="C153" s="10"/>
+      <c r="C153" s="1"/>
       <c r="D153" s="10"/>
       <c r="E153" s="10"/>
-      <c r="I153" s="10"/>
-    </row>
-    <row r="154" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F153" s="10"/>
+      <c r="J153" s="10"/>
+    </row>
+    <row r="154" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
-      <c r="C154" s="10"/>
+      <c r="C154" s="1"/>
       <c r="D154" s="10"/>
       <c r="E154" s="10"/>
-      <c r="I154" s="10"/>
-    </row>
-    <row r="155" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F154" s="10"/>
+      <c r="J154" s="10"/>
+    </row>
+    <row r="155" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
-      <c r="C155" s="10"/>
+      <c r="C155" s="1"/>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
-      <c r="I155" s="10"/>
-    </row>
-    <row r="156" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F155" s="10"/>
+      <c r="J155" s="10"/>
+    </row>
+    <row r="156" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
-      <c r="C156" s="10"/>
+      <c r="C156" s="1"/>
       <c r="D156" s="10"/>
       <c r="E156" s="10"/>
-      <c r="I156" s="10"/>
-    </row>
-    <row r="157" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F156" s="10"/>
+      <c r="J156" s="10"/>
+    </row>
+    <row r="157" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
-      <c r="C157" s="10"/>
+      <c r="C157" s="1"/>
       <c r="D157" s="10"/>
       <c r="E157" s="10"/>
-      <c r="I157" s="10"/>
-    </row>
-    <row r="158" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F157" s="10"/>
+      <c r="J157" s="10"/>
+    </row>
+    <row r="158" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
-      <c r="C158" s="10"/>
+      <c r="C158" s="1"/>
       <c r="D158" s="10"/>
       <c r="E158" s="10"/>
-      <c r="I158" s="10"/>
-    </row>
-    <row r="159" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F158" s="10"/>
+      <c r="J158" s="10"/>
+    </row>
+    <row r="159" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
-      <c r="C159" s="10"/>
+      <c r="C159" s="1"/>
       <c r="D159" s="10"/>
       <c r="E159" s="10"/>
-      <c r="I159" s="10"/>
-    </row>
-    <row r="160" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F159" s="10"/>
+      <c r="J159" s="10"/>
+    </row>
+    <row r="160" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
-      <c r="C160" s="10"/>
+      <c r="C160" s="1"/>
       <c r="D160" s="10"/>
       <c r="E160" s="10"/>
-      <c r="I160" s="10"/>
-    </row>
-    <row r="161" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F160" s="10"/>
+      <c r="J160" s="10"/>
+    </row>
+    <row r="161" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
-      <c r="C161" s="10"/>
+      <c r="C161" s="1"/>
       <c r="D161" s="10"/>
       <c r="E161" s="10"/>
-      <c r="I161" s="10"/>
-    </row>
-    <row r="162" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F161" s="10"/>
+      <c r="J161" s="10"/>
+    </row>
+    <row r="162" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
-      <c r="C162" s="10"/>
+      <c r="C162" s="1"/>
       <c r="D162" s="10"/>
       <c r="E162" s="10"/>
-      <c r="I162" s="10"/>
-    </row>
-    <row r="163" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F162" s="10"/>
+      <c r="J162" s="10"/>
+    </row>
+    <row r="163" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="10"/>
+      <c r="C163" s="1"/>
       <c r="D163" s="10"/>
       <c r="E163" s="10"/>
-      <c r="I163" s="10"/>
-    </row>
-    <row r="164" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F163" s="10"/>
+      <c r="J163" s="10"/>
+    </row>
+    <row r="164" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="10"/>
+      <c r="C164" s="1"/>
       <c r="D164" s="10"/>
       <c r="E164" s="10"/>
-      <c r="I164" s="10"/>
-    </row>
-    <row r="165" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F164" s="10"/>
+      <c r="J164" s="10"/>
+    </row>
+    <row r="165" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
-      <c r="C165" s="10"/>
+      <c r="C165" s="1"/>
       <c r="D165" s="10"/>
       <c r="E165" s="10"/>
-      <c r="I165" s="10"/>
-    </row>
-    <row r="166" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F165" s="10"/>
+      <c r="J165" s="10"/>
+    </row>
+    <row r="166" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
-      <c r="C166" s="10"/>
+      <c r="C166" s="1"/>
       <c r="D166" s="10"/>
       <c r="E166" s="10"/>
-      <c r="I166" s="10"/>
-    </row>
-    <row r="167" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F166" s="10"/>
+      <c r="J166" s="10"/>
+    </row>
+    <row r="167" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
-      <c r="C167" s="10"/>
+      <c r="C167" s="1"/>
       <c r="D167" s="10"/>
       <c r="E167" s="10"/>
-      <c r="I167" s="10"/>
-    </row>
-    <row r="168" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F167" s="10"/>
+      <c r="J167" s="10"/>
+    </row>
+    <row r="168" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
-      <c r="C168" s="10"/>
+      <c r="C168" s="1"/>
       <c r="D168" s="10"/>
       <c r="E168" s="10"/>
-      <c r="I168" s="10"/>
-    </row>
-    <row r="169" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F168" s="10"/>
+      <c r="J168" s="10"/>
+    </row>
+    <row r="169" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
-      <c r="C169" s="10"/>
+      <c r="C169" s="1"/>
       <c r="D169" s="10"/>
       <c r="E169" s="10"/>
-      <c r="I169" s="10"/>
-    </row>
-    <row r="170" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F169" s="10"/>
+      <c r="J169" s="10"/>
+    </row>
+    <row r="170" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
-      <c r="C170" s="10"/>
+      <c r="C170" s="1"/>
       <c r="D170" s="10"/>
       <c r="E170" s="10"/>
-      <c r="I170" s="10"/>
-    </row>
-    <row r="171" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F170" s="10"/>
+      <c r="J170" s="10"/>
+    </row>
+    <row r="171" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
-      <c r="C171" s="10"/>
+      <c r="C171" s="1"/>
       <c r="D171" s="10"/>
       <c r="E171" s="10"/>
-      <c r="I171" s="10"/>
-    </row>
-    <row r="172" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F171" s="10"/>
+      <c r="J171" s="10"/>
+    </row>
+    <row r="172" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
-      <c r="C172" s="10"/>
+      <c r="C172" s="1"/>
       <c r="D172" s="10"/>
       <c r="E172" s="10"/>
-      <c r="I172" s="10"/>
-    </row>
-    <row r="173" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F172" s="10"/>
+      <c r="J172" s="10"/>
+    </row>
+    <row r="173" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
-      <c r="C173" s="10"/>
+      <c r="C173" s="1"/>
       <c r="D173" s="10"/>
       <c r="E173" s="10"/>
-      <c r="I173" s="10"/>
-    </row>
-    <row r="174" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F173" s="10"/>
+      <c r="J173" s="10"/>
+    </row>
+    <row r="174" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
-      <c r="C174" s="10"/>
+      <c r="C174" s="1"/>
       <c r="D174" s="10"/>
       <c r="E174" s="10"/>
-      <c r="I174" s="10"/>
-    </row>
-    <row r="175" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F174" s="10"/>
+      <c r="J174" s="10"/>
+    </row>
+    <row r="175" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
-      <c r="C175" s="10"/>
+      <c r="C175" s="1"/>
       <c r="D175" s="10"/>
       <c r="E175" s="10"/>
-      <c r="I175" s="10"/>
-    </row>
-    <row r="176" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F175" s="10"/>
+      <c r="J175" s="10"/>
+    </row>
+    <row r="176" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
-      <c r="C176" s="10"/>
+      <c r="C176" s="1"/>
       <c r="D176" s="10"/>
       <c r="E176" s="10"/>
-      <c r="I176" s="10"/>
-    </row>
-    <row r="177" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F176" s="10"/>
+      <c r="J176" s="10"/>
+    </row>
+    <row r="177" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
-      <c r="C177" s="10"/>
+      <c r="C177" s="1"/>
       <c r="D177" s="10"/>
       <c r="E177" s="10"/>
-      <c r="I177" s="10"/>
-    </row>
-    <row r="178" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F177" s="10"/>
+      <c r="J177" s="10"/>
+    </row>
+    <row r="178" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
-      <c r="C178" s="10"/>
+      <c r="C178" s="1"/>
       <c r="D178" s="10"/>
       <c r="E178" s="10"/>
-      <c r="I178" s="10"/>
-    </row>
-    <row r="179" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F178" s="10"/>
+      <c r="J178" s="10"/>
+    </row>
+    <row r="179" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
-      <c r="C179" s="10"/>
+      <c r="C179" s="1"/>
       <c r="D179" s="10"/>
       <c r="E179" s="10"/>
-      <c r="I179" s="10"/>
-    </row>
-    <row r="180" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F179" s="10"/>
+      <c r="J179" s="10"/>
+    </row>
+    <row r="180" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
-      <c r="C180" s="10"/>
+      <c r="C180" s="1"/>
       <c r="D180" s="10"/>
       <c r="E180" s="10"/>
-      <c r="I180" s="10"/>
-    </row>
-    <row r="181" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F180" s="10"/>
+      <c r="J180" s="10"/>
+    </row>
+    <row r="181" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
-      <c r="C181" s="10"/>
+      <c r="C181" s="1"/>
       <c r="D181" s="10"/>
       <c r="E181" s="10"/>
-      <c r="I181" s="10"/>
-    </row>
-    <row r="182" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F181" s="10"/>
+      <c r="J181" s="10"/>
+    </row>
+    <row r="182" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
-      <c r="C182" s="10"/>
+      <c r="C182" s="1"/>
       <c r="D182" s="10"/>
       <c r="E182" s="10"/>
-      <c r="I182" s="10"/>
-    </row>
-    <row r="183" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F182" s="10"/>
+      <c r="J182" s="10"/>
+    </row>
+    <row r="183" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
-      <c r="C183" s="10"/>
+      <c r="C183" s="1"/>
       <c r="D183" s="10"/>
       <c r="E183" s="10"/>
-      <c r="I183" s="10"/>
-    </row>
-    <row r="184" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F183" s="10"/>
+      <c r="J183" s="10"/>
+    </row>
+    <row r="184" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
-      <c r="D184" s="10"/>
-      <c r="I184" s="10"/>
-    </row>
-    <row r="185" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C184" s="1"/>
+      <c r="E184" s="10"/>
+      <c r="J184" s="10"/>
+    </row>
+    <row r="185" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
-      <c r="D185" s="10"/>
-      <c r="I185" s="10"/>
-    </row>
-    <row r="186" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C185" s="1"/>
+      <c r="E185" s="10"/>
+      <c r="J185" s="10"/>
+    </row>
+    <row r="186" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
-      <c r="D186" s="10"/>
-      <c r="I186" s="10"/>
+      <c r="C186" s="1"/>
+      <c r="E186" s="10"/>
+      <c r="J186" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ABDE0B-39C0-406D-B0B7-AFFB5102BCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDF6114-A674-45C2-84F2-F02953CD2F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,16 +272,16 @@
     <t>color</t>
   </si>
   <si>
-    <t>red</t>
-  </si>
-  <si>
-    <t>green</t>
-  </si>
-  <si>
-    <t>blue</t>
-  </si>
-  <si>
-    <t>yellow</t>
+    <t>rgba(255,0,255, 0.8)</t>
+  </si>
+  <si>
+    <t>rgba(0,255,0, 0.4)</t>
+  </si>
+  <si>
+    <t>rgba(0,100,255,0.4)</t>
+  </si>
+  <si>
+    <t>rgba(0,0,0, 0.4)</t>
   </si>
 </sst>
 </file>
@@ -521,7 +521,8 @@
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2" max="3" width="11.5546875" style="2"/>
+    <col min="2" max="2" width="11.5546875" style="2"/>
+    <col min="3" max="3" width="19" style="2" customWidth="1"/>
     <col min="4" max="6" width="11.5546875" style="11"/>
     <col min="7" max="9" width="11.5546875" style="2"/>
     <col min="10" max="10" width="11.5546875" style="11"/>
@@ -571,7 +572,7 @@
         <v>69</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -604,7 +605,7 @@
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -637,7 +638,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -670,7 +671,7 @@
         <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -937,7 +938,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" s="8">
         <v>150</v>
@@ -976,7 +977,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="8">
         <v>150</v>
@@ -1015,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" s="8">
         <v>150</v>
@@ -1054,7 +1055,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" s="8">
         <v>150</v>
@@ -1093,7 +1094,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" s="8">
         <v>150</v>
@@ -1229,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D20" s="8">
         <v>200</v>
@@ -1268,7 +1269,7 @@
         <v>61</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D21" s="8">
         <v>200</v>
@@ -1308,7 +1309,7 @@
         <v>62</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D22" s="8">
         <v>100</v>
@@ -1345,7 +1346,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" s="8">
         <v>150</v>
@@ -1384,7 +1385,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" s="8">
         <v>204</v>
@@ -1423,7 +1424,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D25" s="8">
         <v>200</v>
@@ -1462,7 +1463,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D26" s="8">
         <v>250</v>
@@ -1501,7 +1502,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27" s="8">
         <v>125</v>
@@ -1642,7 +1643,7 @@
         <v>EI-7x2</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D31" s="8">
         <v>100</v>
@@ -1718,7 +1719,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="8">
         <v>100</v>
@@ -1757,7 +1758,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" s="8">
         <v>204</v>
@@ -1796,7 +1797,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" s="8">
         <v>80</v>
@@ -1835,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D36" s="8">
         <v>50</v>
@@ -1952,7 +1953,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D39" s="8">
         <v>125</v>
@@ -1991,7 +1992,7 @@
         <v>32</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D40" s="8">
         <v>200</v>
@@ -2030,7 +2031,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D41" s="8">
         <v>80</v>
@@ -2069,7 +2070,7 @@
         <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D42" s="8">
         <v>80</v>
@@ -2108,7 +2109,7 @@
         <v>35</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D43" s="8">
         <v>50</v>
@@ -2147,7 +2148,7 @@
         <v>36</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D44" s="8">
         <v>50</v>
@@ -2186,7 +2187,7 @@
         <v>64</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D45" s="8">
         <v>65</v>
@@ -2225,7 +2226,7 @@
         <v>65</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D46" s="8">
         <v>65</v>
@@ -2264,7 +2265,7 @@
         <v>66</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D47" s="8">
         <v>50</v>
@@ -2303,7 +2304,7 @@
         <v>67</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D48" s="8">
         <v>50</v>
@@ -2342,7 +2343,7 @@
         <v>37</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D49" s="8">
         <v>32</v>
@@ -2381,7 +2382,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D50" s="8">
         <v>80</v>
@@ -2420,7 +2421,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D51" s="8">
         <v>125</v>
@@ -2459,7 +2460,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D52" s="8">
         <v>50</v>
@@ -2498,7 +2499,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D53" s="8">
         <v>50</v>
@@ -2537,7 +2538,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D54" s="8">
         <v>43</v>
@@ -2574,7 +2575,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D55" s="8">
         <v>40</v>
@@ -2611,7 +2612,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D56" s="8">
         <v>100</v>
@@ -2648,7 +2649,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D57" s="8">
         <v>50</v>
@@ -2687,7 +2688,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D58" s="8">
         <v>80</v>
@@ -2726,7 +2727,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D59" s="8">
         <v>50</v>
@@ -2765,7 +2766,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D60" s="8">
         <v>50</v>
@@ -2802,7 +2803,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D61" s="8">
         <v>50</v>
@@ -2839,7 +2840,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D62" s="8">
         <v>73</v>
@@ -2878,7 +2879,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D63" s="8">
         <v>65</v>
@@ -2917,7 +2918,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D64" s="8">
         <v>125</v>
@@ -2956,7 +2957,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D65" s="8">
         <v>125</v>
@@ -2995,7 +2996,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D66" s="8">
         <v>80</v>
@@ -3034,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D67" s="8">
         <v>80</v>
@@ -3073,7 +3074,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D68" s="8">
         <v>80</v>
@@ -3113,7 +3114,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D69" s="8">
         <v>65</v>
@@ -3152,7 +3153,7 @@
         <v>12</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D70" s="8">
         <v>129</v>
@@ -3191,7 +3192,7 @@
         <v>13</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D71" s="8">
         <v>129</v>
@@ -3230,7 +3231,7 @@
         <v>14</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D72" s="8">
         <v>100</v>

--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8ACEBC-14AC-477D-88E5-BC441E517BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E59D8A-2CEB-4E1C-BBA2-1F645DDB53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="86">
   <si>
     <t>source</t>
   </si>
@@ -62,9 +62,6 @@
     <t>SIL-PEL</t>
   </si>
   <si>
-    <t>LIQ-LIQ</t>
-  </si>
-  <si>
     <t>Y-120</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>colector</t>
   </si>
   <si>
-    <t>GF-ass</t>
-  </si>
-  <si>
     <t>nautas</t>
   </si>
   <si>
@@ -249,6 +243,60 @@
   </si>
   <si>
     <t>rgba(255,255,0,0.4)</t>
+  </si>
+  <si>
+    <t>L-660</t>
+  </si>
+  <si>
+    <t>L-670</t>
+  </si>
+  <si>
+    <t>esquema</t>
+  </si>
+  <si>
+    <t>Y-190</t>
+  </si>
+  <si>
+    <t>Y-180</t>
+  </si>
+  <si>
+    <t>SS-3000</t>
+  </si>
+  <si>
+    <t>SS-1000</t>
+  </si>
+  <si>
+    <t>S-600</t>
+  </si>
+  <si>
+    <t>S-2100/S-2200</t>
+  </si>
+  <si>
+    <t>S-6000</t>
+  </si>
+  <si>
+    <t>SI-603</t>
+  </si>
+  <si>
+    <t>SR-601</t>
+  </si>
+  <si>
+    <t>SI-2107</t>
+  </si>
+  <si>
+    <t>SI-2207</t>
+  </si>
+  <si>
+    <t>SI-6002</t>
+  </si>
+  <si>
+    <t>SS-2200</t>
+  </si>
+  <si>
+    <t>SS-2100</t>
+  </si>
+  <si>
+    <t>GF-ASS</t>
   </si>
 </sst>
 </file>
@@ -329,14 +377,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,17 +514,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="6"/>
-    <col min="3" max="3" width="19" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="6"/>
-    <col min="5" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="1"/>
+    <col min="3" max="3" width="19" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -485,969 +531,1281 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="4">
-        <v>100.46507000896433</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="4">
+        <v>65</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="4">
+        <v>203</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4">
+        <v>222</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="4">
+        <v>191</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4">
+        <v>205</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="4">
+        <v>231</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="4">
+        <v>75</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4">
+        <v>72</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="4">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="4">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="4">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="4">
-        <v>56.384974069999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="4">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D13" s="4">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>129.48513944741836</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="4">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D16" s="4">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>129.48513944741836</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="4">
+        <v>100.46507000896433</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="4">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="4">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="C19" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19" s="4">
-        <v>101.8421149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="4">
-        <v>32.801418630000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>32.979183040324209</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D21" s="4">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>42.5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D22" s="4">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>79.605544469999998</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23" s="4">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>22.236570419999996</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D24" s="4">
+        <v>8.3366590708646733</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="4">
+        <v>28.217898310000002</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="4">
+        <v>20.000000000000004</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="4">
+        <v>41</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="4">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="4">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="4">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="4">
-        <v>79.605544469999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="C29" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29" s="4">
-        <v>22.236570419999996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D30" s="4">
-        <v>20.000000000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D31" s="4">
         <v>10.190084069999997</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="4">
+        <v>32.801418630000001</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="4">
+        <v>67</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="4">
+        <v>44</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="4">
+        <v>47</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="4">
+        <v>150</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="4">
+        <v>23.5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="4">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="4">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="4">
-        <v>13.601897040000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="C38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="4">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="4">
-        <v>15.34166403</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="4">
-        <v>13.89928536</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D39" s="4">
-        <v>25.380859569999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>56.384974069999998</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D40" s="4">
-        <v>17.134670450000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>30.4</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D41" s="4">
-        <v>28.217898310000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>13.8940359441001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D42" s="4">
-        <v>10.822828879999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D43" s="4">
-        <v>8.1686317729999995</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>13.601897040000001</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D44" s="4">
         <v>10.822828879999999</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="4">
+        <v>32.979183040324209</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D45" s="4">
-        <v>1.17621229</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
+      <c r="D48" s="4">
+        <v>3.8707563084879837</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="4">
+        <v>5.0590982872275125</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="4">
+        <v>8.1686317729999995</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="4">
+        <v>32.979183040324209</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="4">
-        <v>129.48513944741836</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
+      <c r="B52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="4">
-        <v>129.48513944741836</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="4">
-        <v>32.979183040324209</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="4">
-        <v>19.43128149161133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" s="4">
-        <v>19.43128149161133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="B53" s="4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D54" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+        <v>10.822828879999999</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D55" s="4">
         <v>8.3366590708646733</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" s="4">
+        <v>101.8421149</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="4">
+        <v>28</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D65" s="4">
+        <v>8.3366590708646733</v>
+      </c>
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66" s="4">
+        <v>8.3366590708646733</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="4">
+        <v>15.34166403</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" s="4">
+        <v>13.89928536</v>
+      </c>
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1.17621229</v>
+      </c>
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="4">
+        <v>19.43128149161133</v>
+      </c>
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D71" s="4">
+        <v>19.43128149161133</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72" s="4">
+        <v>8.3366590708646733</v>
+      </c>
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="4">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" s="4">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B57" s="4" t="s">
+      <c r="C75" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="4">
+        <v>17.134670450000002</v>
+      </c>
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="4">
-        <v>8.3366590708646733</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" s="4">
-        <v>5.0590982872275125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="4">
-        <v>3.8707563084879837</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" s="4">
-        <v>32.979183040324209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="4">
-        <v>32.979183040324209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="4">
-        <v>13.8940359441001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-    </row>
-    <row r="65" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C76" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" s="4">
+        <v>25.380859569999998</v>
+      </c>
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
     </row>
-    <row r="78" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
     </row>
-    <row r="79" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
     </row>
-    <row r="80" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2029,10 +2387,22 @@
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
     </row>
+    <row r="177" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="5"/>
+    </row>
+    <row r="178" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="5"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D72">
-      <sortCondition ref="C1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D77">
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E59D8A-2CEB-4E1C-BBA2-1F645DDB53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8880D3B-5CD7-439D-85EC-8D7586C9A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="99">
   <si>
     <t>source</t>
   </si>
@@ -297,6 +297,45 @@
   </si>
   <si>
     <t>GF-ASS</t>
+  </si>
+  <si>
+    <t>Y-190-1</t>
+  </si>
+  <si>
+    <t>Y-190-2</t>
+  </si>
+  <si>
+    <t>Y-180-3</t>
+  </si>
+  <si>
+    <t>Y-180-4</t>
+  </si>
+  <si>
+    <t>SS-300001</t>
+  </si>
+  <si>
+    <t>SS-100002</t>
+  </si>
+  <si>
+    <t>SI-6031</t>
+  </si>
+  <si>
+    <t>SI-210701</t>
+  </si>
+  <si>
+    <t>SI-220702</t>
+  </si>
+  <si>
+    <t>SI-2x0703</t>
+  </si>
+  <si>
+    <t>SS-210004</t>
+  </si>
+  <si>
+    <t>SS-220005</t>
+  </si>
+  <si>
+    <t>S-60021</t>
   </si>
 </sst>
 </file>
@@ -514,7 +553,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
@@ -715,7 +754,8 @@
         <v>65</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <f>SUM(D77:D79)</f>
+        <v>78.997951654825172</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -817,7 +857,8 @@
         <v>65</v>
       </c>
       <c r="D18" s="4">
-        <v>0</v>
+        <f>SUM(D84:D85)</f>
+        <v>15.944518911578967</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -1788,120 +1829,299 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
+      <c r="A77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D77" s="4">
+        <f>SUM(D89:D91)</f>
+        <v>34.817325760346947</v>
+      </c>
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
+      <c r="A78" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D78" s="4">
+        <f>D86</f>
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
+      <c r="A79" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79" s="4">
+        <f>D92</f>
+        <v>30.75820583953503</v>
+      </c>
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-    </row>
-    <row r="84" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-    </row>
-    <row r="87" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-    </row>
-    <row r="90" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-    </row>
-    <row r="91" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D81" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D82" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" s="4">
+        <v>13.422420054943197</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D89" s="4">
+        <v>18.872806848767983</v>
+      </c>
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D90" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D91" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="4">
+        <v>30.75820583953503</v>
+      </c>
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
     </row>
-    <row r="94" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
     </row>
-    <row r="95" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
     </row>
-    <row r="96" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2398,6 +2618,12 @@
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
+    </row>
+    <row r="179" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/data/sankey/sankey_nodes-at.xlsx
+++ b/data/sankey/sankey_nodes-at.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ArnauCoronado\Documents_local\euromed\sxs\data\sankey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8880D3B-5CD7-439D-85EC-8D7586C9A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955A0B3E-E89C-4758-A9C0-CBCDEE883CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="101">
   <si>
     <t>source</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>S-60021</t>
+  </si>
+  <si>
+    <t>R-150</t>
+  </si>
+  <si>
+    <t>rgba(255,255, 0, 0.4)</t>
   </si>
 </sst>
 </file>
@@ -553,7 +559,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
@@ -754,7 +760,7 @@
         <v>65</v>
       </c>
       <c r="D12" s="4">
-        <f>SUM(D77:D79)</f>
+        <f>SUM(D78:D80)</f>
         <v>78.997951654825172</v>
       </c>
       <c r="E12" s="1">
@@ -857,7 +863,7 @@
         <v>65</v>
       </c>
       <c r="D18" s="4">
-        <f>SUM(D84:D85)</f>
+        <f>SUM(D85:D86)</f>
         <v>15.944518911578967</v>
       </c>
       <c r="E18" s="1">
@@ -1325,15 +1331,17 @@
     </row>
     <row r="46" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="D46" s="4">
+        <v>18.5</v>
+      </c>
       <c r="E46" s="1">
         <v>1</v>
       </c>
@@ -1343,7 +1351,7 @@
         <v>85</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>65</v>
@@ -1355,17 +1363,15 @@
     </row>
     <row r="48" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="4">
-        <v>3.8707563084879837</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D48" s="4"/>
       <c r="E48" s="1">
         <v>1</v>
       </c>
@@ -1375,13 +1381,13 @@
         <v>68</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D49" s="4">
-        <v>5.0590982872275125</v>
+        <v>3.8707563084879837</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -1389,16 +1395,16 @@
     </row>
     <row r="50" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D50" s="4">
-        <v>8.1686317729999995</v>
+        <v>5.0590982872275125</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -1409,13 +1415,13 @@
         <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D51" s="4">
-        <v>32.979183040324209</v>
+        <v>8.1686317729999995</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -1423,15 +1429,17 @@
     </row>
     <row r="52" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="D52" s="4">
+        <v>32.979183040324209</v>
+      </c>
       <c r="E52" s="1">
         <v>1</v>
       </c>
@@ -1441,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>65</v>
@@ -1453,17 +1461,15 @@
     </row>
     <row r="54" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="4">
-        <v>10.822828879999999</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="1">
         <v>1</v>
       </c>
@@ -1473,13 +1479,13 @@
         <v>21</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D55" s="4">
-        <v>8.3366590708646733</v>
+        <v>10.822828879999999</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -1487,16 +1493,16 @@
     </row>
     <row r="56" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D56" s="4">
-        <v>101.8421149</v>
+        <v>8.3366590708646733</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -1507,13 +1513,13 @@
         <v>5</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D57" s="4">
-        <v>28</v>
+        <v>101.8421149</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -1521,15 +1527,17 @@
     </row>
     <row r="58" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="D58" s="4">
+        <v>28</v>
+      </c>
       <c r="E58" s="1">
         <v>1</v>
       </c>
@@ -1539,7 +1547,7 @@
         <v>76</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>65</v>
@@ -1554,7 +1562,7 @@
         <v>76</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>65</v>
@@ -1569,7 +1577,7 @@
         <v>76</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>65</v>
@@ -1581,10 +1589,10 @@
     </row>
     <row r="62" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>65</v>
@@ -1599,22 +1607,22 @@
         <v>75</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D63" s="4"/>
-      <c r="E63" s="4">
+      <c r="E63" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>65</v>
@@ -1626,17 +1634,15 @@
     </row>
     <row r="65" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D65" s="4">
-        <v>8.3366590708646733</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D65" s="4"/>
       <c r="E65" s="4">
         <v>1</v>
       </c>
@@ -1646,7 +1652,7 @@
         <v>6</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>66</v>
@@ -1663,13 +1669,13 @@
         <v>6</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D67" s="4">
-        <v>15.34166403</v>
+        <v>8.3366590708646733</v>
       </c>
       <c r="E67" s="4">
         <v>1</v>
@@ -1680,13 +1686,13 @@
         <v>6</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D68" s="4">
-        <v>13.89928536</v>
+        <v>15.34166403</v>
       </c>
       <c r="E68" s="4">
         <v>1</v>
@@ -1697,13 +1703,13 @@
         <v>6</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D69" s="4">
-        <v>1.17621229</v>
+        <v>13.89928536</v>
       </c>
       <c r="E69" s="4">
         <v>1</v>
@@ -1711,16 +1717,16 @@
     </row>
     <row r="70" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D70" s="4">
-        <v>19.43128149161133</v>
+        <v>1.17621229</v>
       </c>
       <c r="E70" s="4">
         <v>1</v>
@@ -1728,10 +1734,10 @@
     </row>
     <row r="71" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>66</v>
@@ -1748,13 +1754,13 @@
         <v>22</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D72" s="4">
-        <v>8.3366590708646733</v>
+        <v>19.43128149161133</v>
       </c>
       <c r="E72" s="4">
         <v>1</v>
@@ -1762,16 +1768,16 @@
     </row>
     <row r="73" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D73" s="4">
-        <v>0</v>
+        <v>8.3366590708646733</v>
       </c>
       <c r="E73" s="4">
         <v>1</v>
@@ -1782,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>66</v>
@@ -1799,13 +1805,13 @@
         <v>14</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D75" s="4">
-        <v>17.134670450000002</v>
+        <v>0</v>
       </c>
       <c r="E75" s="4">
         <v>1</v>
@@ -1816,13 +1822,13 @@
         <v>14</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D76" s="4">
-        <v>25.380859569999998</v>
+        <v>17.134670450000002</v>
       </c>
       <c r="E76" s="4">
         <v>1</v>
@@ -1830,17 +1836,16 @@
     </row>
     <row r="77" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D77" s="4">
-        <f>SUM(D89:D91)</f>
-        <v>34.817325760346947</v>
+        <v>25.380859569999998</v>
       </c>
       <c r="E77" s="4">
         <v>1</v>
@@ -1851,14 +1856,14 @@
         <v>12</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D78" s="4">
-        <f>D86</f>
-        <v>13.422420054943197</v>
+        <f>SUM(D90:D92)</f>
+        <v>34.817325760346947</v>
       </c>
       <c r="E78" s="4">
         <v>1</v>
@@ -1869,14 +1874,14 @@
         <v>12</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D79" s="4">
-        <f>D92</f>
-        <v>30.75820583953503</v>
+        <f>D87</f>
+        <v>13.422420054943197</v>
       </c>
       <c r="E79" s="4">
         <v>1</v>
@@ -1884,16 +1889,17 @@
     </row>
     <row r="80" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D80" s="4">
-        <v>13.422420054943197</v>
+        <f>D93</f>
+        <v>30.75820583953503</v>
       </c>
       <c r="E80" s="4">
         <v>1</v>
@@ -1904,7 +1910,7 @@
         <v>85</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>65</v>
@@ -1921,7 +1927,7 @@
         <v>85</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>65</v>
@@ -1938,7 +1944,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>65</v>
@@ -1952,16 +1958,16 @@
     </row>
     <row r="84" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="4" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D84" s="4">
-        <v>7.9722594557894837</v>
+        <v>13.422420054943197</v>
       </c>
       <c r="E84" s="4">
         <v>1</v>
@@ -1972,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>65</v>
@@ -1986,16 +1992,16 @@
     </row>
     <row r="86" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="4" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D86" s="4">
-        <v>13.422420054943197</v>
+        <v>7.9722594557894837</v>
       </c>
       <c r="E86" s="4">
         <v>1</v>
@@ -2003,10 +2009,10 @@
     </row>
     <row r="87" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>65</v>
@@ -2023,13 +2029,13 @@
         <v>76</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D88" s="4">
-        <v>7.9722594557894837</v>
+        <v>13.422420054943197</v>
       </c>
       <c r="E88" s="4">
         <v>1</v>
@@ -2040,13 +2046,13 @@
         <v>76</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D89" s="4">
-        <v>18.872806848767983</v>
+        <v>7.9722594557894837</v>
       </c>
       <c r="E89" s="4">
         <v>1</v>
@@ -2057,13 +2063,13 @@
         <v>76</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D90" s="4">
-        <v>7.9722594557894837</v>
+        <v>18.872806848767983</v>
       </c>
       <c r="E90" s="4">
         <v>1</v>
@@ -2074,7 +2080,7 @@
         <v>76</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>65</v>
@@ -2088,26 +2094,37 @@
     </row>
     <row r="92" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="4">
+        <v>7.9722594557894837</v>
+      </c>
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B93" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D92" s="4">
+      <c r="C93" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D93" s="4">
         <v>30.75820583953503</v>
       </c>
-      <c r="E92" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5"/>
@@ -2624,6 +2641,12 @@
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
+    </row>
+    <row r="180" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="5"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
